--- a/database/event/3133/event_3133_evp_summary.xlsx
+++ b/database/event/3133/event_3133_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.4468</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5019</v>
+        <v>3.4252</v>
       </c>
       <c r="E2" t="n">
         <v>9.711600000000001</v>
@@ -548,7 +548,7 @@
         <v>3.1927</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3955</v>
+        <v>2.3341</v>
       </c>
       <c r="E3" t="n">
         <v>6.9728</v>
@@ -594,7 +594,7 @@
         <v>2.939</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1716</v>
+        <v>2.1133</v>
       </c>
       <c r="E4" t="n">
         <v>6.4186</v>
@@ -640,7 +640,7 @@
         <v>2.2417</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5565</v>
+        <v>1.5066</v>
       </c>
       <c r="E5" t="n">
         <v>4.8959</v>
@@ -686,7 +686,7 @@
         <v>1.9104</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2642</v>
+        <v>1.2183</v>
       </c>
       <c r="E6" t="n">
         <v>4.1723</v>
@@ -732,7 +732,7 @@
         <v>1.8174</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1821</v>
+        <v>1.1374</v>
       </c>
       <c r="E7" t="n">
         <v>3.9691</v>
@@ -778,7 +778,7 @@
         <v>1.7384</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1124</v>
+        <v>1.0687</v>
       </c>
       <c r="E8" t="n">
         <v>3.7967</v>
@@ -824,7 +824,7 @@
         <v>1.7264</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1018</v>
+        <v>1.0582</v>
       </c>
       <c r="E9" t="n">
         <v>3.7703</v>
@@ -870,7 +870,7 @@
         <v>1.6526</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0367</v>
+        <v>0.994</v>
       </c>
       <c r="E10" t="n">
         <v>3.6092</v>
@@ -916,7 +916,7 @@
         <v>1.6516</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0358</v>
+        <v>0.9932</v>
       </c>
       <c r="E11" t="n">
         <v>3.6071</v>
@@ -962,7 +962,7 @@
         <v>1.389</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8041</v>
+        <v>0.7647</v>
       </c>
       <c r="E12" t="n">
         <v>3.0336</v>
@@ -1008,7 +1008,7 @@
         <v>1.2595</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6899</v>
+        <v>0.652</v>
       </c>
       <c r="E13" t="n">
         <v>2.7508</v>
@@ -1054,7 +1054,7 @@
         <v>1.2415</v>
       </c>
       <c r="D14" t="n">
-        <v>0.674</v>
+        <v>0.6364</v>
       </c>
       <c r="E14" t="n">
         <v>2.7115</v>
@@ -1100,7 +1100,7 @@
         <v>1.079</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5306</v>
+        <v>0.4949</v>
       </c>
       <c r="E15" t="n">
         <v>2.3565</v>
@@ -1146,7 +1146,7 @@
         <v>0.9199000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3903</v>
+        <v>0.3565</v>
       </c>
       <c r="E16" t="n">
         <v>2.0091</v>
@@ -1192,7 +1192,7 @@
         <v>0.7284</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2213</v>
+        <v>0.1899</v>
       </c>
       <c r="E17" t="n">
         <v>1.5908</v>
@@ -1238,7 +1238,7 @@
         <v>0.5627</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0751</v>
+        <v>0.0457</v>
       </c>
       <c r="E18" t="n">
         <v>1.229</v>
@@ -1284,7 +1284,7 @@
         <v>0.5303</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0465</v>
+        <v>0.0175</v>
       </c>
       <c r="E19" t="n">
         <v>1.1582</v>
@@ -1330,7 +1330,7 @@
         <v>0.5236</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0406</v>
+        <v>0.0117</v>
       </c>
       <c r="E20" t="n">
         <v>1.1435</v>
@@ -1376,7 +1376,7 @@
         <v>0.5082</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0271</v>
+        <v>-0.0017</v>
       </c>
       <c r="E21" t="n">
         <v>1.11</v>
@@ -1422,7 +1422,7 @@
         <v>0.3941</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0737</v>
+        <v>-0.101</v>
       </c>
       <c r="E22" t="n">
         <v>0.8606</v>
@@ -1468,7 +1468,7 @@
         <v>0.3104</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1475</v>
+        <v>-0.1738</v>
       </c>
       <c r="E23" t="n">
         <v>0.678</v>
@@ -1514,7 +1514,7 @@
         <v>0.2109</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2353</v>
+        <v>-0.2604</v>
       </c>
       <c r="E24" t="n">
         <v>0.4606</v>
@@ -1560,7 +1560,7 @@
         <v>0.0411</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3851</v>
+        <v>-0.4082</v>
       </c>
       <c r="E25" t="n">
         <v>0.0897</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1111</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5194</v>
+        <v>-0.5406</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2427</v>
@@ -1652,7 +1652,7 @@
         <v>-0.171</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5722</v>
+        <v>-0.5927</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3735</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1742</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.575</v>
+        <v>-0.5955</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3804</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2313</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6452</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5052</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2759</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6026</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3484</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7288</v>
+        <v>-0.7471</v>
       </c>
       <c r="E31" t="n">
         <v>-0.761</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4018</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7759</v>
+        <v>-0.7935</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8776</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4222</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.8113</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9221</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4338</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8041</v>
+        <v>-0.8214</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9474</v>
@@ -2020,7 +2020,7 @@
         <v>-0.5652</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.92</v>
+        <v>-0.9357</v>
       </c>
       <c r="E35" t="n">
         <v>-1.2343</v>
@@ -2066,7 +2066,7 @@
         <v>-0.6619</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0053</v>
+        <v>-1.0198</v>
       </c>
       <c r="E36" t="n">
         <v>-1.4455</v>
@@ -2112,7 +2112,7 @@
         <v>-0.6945</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0341</v>
+        <v>-1.0482</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5167</v>
@@ -2158,7 +2158,7 @@
         <v>-0.7724</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1028</v>
+        <v>-1.1159</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6868</v>
@@ -2204,7 +2204,7 @@
         <v>-0.8106</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1366</v>
+        <v>-1.1492</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7704</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8181</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1432</v>
+        <v>-1.1558</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7868</v>
@@ -2296,7 +2296,7 @@
         <v>-1.4202</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6744</v>
+        <v>-1.6796</v>
       </c>
       <c r="E41" t="n">
         <v>-3.1017</v>

--- a/database/event/3133/event_3133_evp_summary.xlsx
+++ b/database/event/3133/event_3133_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.711600000000001</v>
+        <v>8.717499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4468</v>
+        <v>3.9916</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4252</v>
+        <v>3.2975</v>
       </c>
       <c r="E2" t="n">
-        <v>9.711600000000001</v>
+        <v>8.717499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3395</v>
+        <v>3.9369</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3721</v>
+        <v>4.7806</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8983</v>
+        <v>8.385</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9702</v>
+        <v>4.3598</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3721</v>
+        <v>4.7806</v>
       </c>
       <c r="K2" t="n">
         <v>109</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>9.3423</v>
+        <v>9.1404</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9728</v>
+        <v>6.3584</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1927</v>
+        <v>2.9114</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3341</v>
+        <v>2.2325</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9728</v>
+        <v>6.3584</v>
       </c>
       <c r="F3" t="n">
-        <v>4.359</v>
+        <v>4.0138</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6138</v>
+        <v>2.3446</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9767</v>
+        <v>8.655799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0337</v>
+        <v>4.5006</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6138</v>
+        <v>2.3446</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.647499999999999</v>
+        <v>6.8452</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4186</v>
+        <v>6.3504</v>
       </c>
       <c r="C4" t="n">
-        <v>2.939</v>
+        <v>2.9077</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1133</v>
+        <v>2.2289</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4186</v>
+        <v>6.3504</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3165</v>
+        <v>3.9161</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1021</v>
+        <v>2.4343</v>
       </c>
       <c r="H4" t="n">
-        <v>4.806</v>
+        <v>8.3117</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8954</v>
+        <v>4.3217</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1021</v>
+        <v>2.4343</v>
       </c>
       <c r="K4" t="n">
         <v>109</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>5.9975</v>
+        <v>6.756</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8959</v>
+        <v>5.6356</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2417</v>
+        <v>2.5804</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5066</v>
+        <v>1.9062</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8959</v>
+        <v>5.6356</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3892</v>
+        <v>2.8867</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5067</v>
+        <v>2.7489</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3892</v>
+        <v>4.6846</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9365</v>
+        <v>2.4358</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5067</v>
+        <v>2.7489</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4432</v>
+        <v>5.184699999999999</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1723</v>
+        <v>4.1775</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9104</v>
+        <v>1.9128</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2183</v>
+        <v>1.2479</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1723</v>
+        <v>4.1775</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9424</v>
+        <v>3.1103</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2299</v>
+        <v>1.0672</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9424</v>
+        <v>5.4725</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3849</v>
+        <v>2.8454</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2299</v>
+        <v>1.0672</v>
       </c>
       <c r="K6" t="n">
         <v>173</v>
@@ -713,7 +713,7 @@
         <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6148</v>
+        <v>3.9126</v>
       </c>
       <c r="N6" t="n">
         <v>254</v>
@@ -722,170 +722,170 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9691</v>
+        <v>3.6962</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8174</v>
+        <v>1.6924</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1374</v>
+        <v>1.0306</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9691</v>
+        <v>3.6962</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2111</v>
+        <v>4.019</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.242</v>
+        <v>-0.3228</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3817</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5515</v>
+        <v>4.5101</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.242</v>
+        <v>-0.3228</v>
       </c>
       <c r="K7" t="n">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3095</v>
+        <v>4.1873</v>
       </c>
       <c r="N7" t="n">
-        <v>305</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7967</v>
+        <v>3.6518</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7384</v>
+        <v>1.6721</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0687</v>
+        <v>1.0106</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7967</v>
+        <v>3.6518</v>
       </c>
       <c r="F8" t="n">
-        <v>4.368</v>
+        <v>1.5355</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5713</v>
+        <v>2.1163</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0131</v>
+        <v>1.5355</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0633</v>
+        <v>0.7984</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5713</v>
+        <v>2.1163</v>
       </c>
       <c r="K8" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="L8" t="n">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="M8" t="n">
-        <v>3.492</v>
+        <v>2.9147</v>
       </c>
       <c r="N8" t="n">
-        <v>254</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7703</v>
+        <v>3.6478</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7264</v>
+        <v>1.6703</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0582</v>
+        <v>1.0088</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7703</v>
+        <v>3.6478</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7703</v>
+        <v>3.7352</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7703</v>
+        <v>7.6742</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7703</v>
+        <v>3.9902</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7703</v>
+        <v>3.9028</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6092</v>
+        <v>3.6179</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6526</v>
+        <v>1.6566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.994</v>
+        <v>0.9953</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6092</v>
+        <v>3.6179</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6092</v>
+        <v>3.6179</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6092</v>
+        <v>4.5845</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6092</v>
+        <v>4.5845</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6092</v>
+        <v>4.5845</v>
       </c>
       <c r="N10" t="n">
         <v>241</v>
@@ -906,219 +906,219 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6071</v>
+        <v>3.5618</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6516</v>
+        <v>1.6309</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9932</v>
+        <v>0.97</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6071</v>
+        <v>3.5618</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2403</v>
+        <v>2.5016</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6332</v>
+        <v>1.0602</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4992</v>
+        <v>3.3278</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6467</v>
+        <v>1.7303</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6332</v>
+        <v>1.0602</v>
       </c>
       <c r="K11" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0135</v>
+        <v>2.7905</v>
       </c>
       <c r="N11" t="n">
-        <v>254</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0336</v>
+        <v>3.3165</v>
       </c>
       <c r="C12" t="n">
-        <v>1.389</v>
+        <v>1.5186</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7647</v>
+        <v>0.8592</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0336</v>
+        <v>3.3165</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5395</v>
+        <v>3.7069</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4941</v>
+        <v>-0.3904</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5395</v>
+        <v>7.5745</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4373</v>
+        <v>3.9384</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4941</v>
+        <v>-0.3904</v>
       </c>
       <c r="K12" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="L12" t="n">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9314</v>
+        <v>3.548</v>
       </c>
       <c r="N12" t="n">
-        <v>430</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7508</v>
+        <v>3.2815</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2595</v>
+        <v>1.5025</v>
       </c>
       <c r="D13" t="n">
-        <v>0.652</v>
+        <v>0.8434</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7508</v>
+        <v>3.2815</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7097</v>
+        <v>3.2815</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7097</v>
+        <v>3.8459</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1963</v>
+        <v>3.8459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L13" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2374</v>
+        <v>3.8459</v>
       </c>
       <c r="N13" t="n">
-        <v>305</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7115</v>
+        <v>3.0852</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2415</v>
+        <v>1.4127</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6364</v>
+        <v>0.7548</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7115</v>
+        <v>3.0852</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6174</v>
+        <v>2.8734</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9059</v>
+        <v>0.2118</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6174</v>
+        <v>4.6379</v>
       </c>
       <c r="I14" t="n">
-        <v>2.932</v>
+        <v>2.4115</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9059</v>
+        <v>0.2118</v>
       </c>
       <c r="K14" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0261</v>
+        <v>2.6233</v>
       </c>
       <c r="N14" t="n">
-        <v>254</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3565</v>
+        <v>2.741</v>
       </c>
       <c r="C15" t="n">
-        <v>1.079</v>
+        <v>1.2551</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4949</v>
+        <v>0.5994</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3565</v>
+        <v>2.741</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0834</v>
+        <v>3.3468</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7269</v>
+        <v>-0.6058</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0834</v>
+        <v>6.3057</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4992</v>
+        <v>3.2787</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7269</v>
+        <v>-0.6058</v>
       </c>
       <c r="K15" t="n">
         <v>173</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7723</v>
+        <v>2.6729</v>
       </c>
       <c r="N15" t="n">
         <v>254</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0091</v>
+        <v>2.7137</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9199000000000001</v>
+        <v>1.2426</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3565</v>
+        <v>0.5871</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0091</v>
+        <v>2.7137</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1367</v>
+        <v>2.1929</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8724</v>
+        <v>0.5208</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1367</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9213</v>
+        <v>1.1647</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8724</v>
+        <v>0.5208</v>
       </c>
       <c r="K16" t="n">
         <v>198</v>
@@ -1173,7 +1173,7 @@
         <v>232</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7937</v>
+        <v>1.6855</v>
       </c>
       <c r="N16" t="n">
         <v>430</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5908</v>
+        <v>2.6256</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7284</v>
+        <v>1.2022</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1899</v>
+        <v>0.5473</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5908</v>
+        <v>2.6256</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0299</v>
+        <v>3.0933</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5609</v>
+        <v>-0.4677</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0299</v>
+        <v>5.4127</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8348</v>
+        <v>2.8144</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5609</v>
+        <v>-0.4677</v>
       </c>
       <c r="K17" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="L17" t="n">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3957</v>
+        <v>2.3467</v>
       </c>
       <c r="N17" t="n">
-        <v>430</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.229</v>
+        <v>2.0597</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5627</v>
+        <v>0.9431</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0457</v>
+        <v>0.2918</v>
       </c>
       <c r="E18" t="n">
-        <v>1.229</v>
+        <v>2.0597</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5419</v>
+        <v>2.2674</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3129</v>
+        <v>-0.2077</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5419</v>
+        <v>2.5027</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2498</v>
+        <v>1.3013</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3129</v>
+        <v>-0.2077</v>
       </c>
       <c r="K18" t="n">
         <v>242</v>
@@ -1265,7 +1265,7 @@
         <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9369000000000001</v>
+        <v>1.0936</v>
       </c>
       <c r="N18" t="n">
         <v>305</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5303</v>
+        <v>0.673</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0175</v>
+        <v>0.0256</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1582</v>
+        <v>1.4699</v>
       </c>
       <c r="N19" t="n">
         <v>182</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5236</v>
+        <v>0.6237</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0117</v>
+        <v>-0.0231</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1435</v>
+        <v>1.3621</v>
       </c>
       <c r="N20" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5082</v>
+        <v>0.5946</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0017</v>
+        <v>-0.0518</v>
       </c>
       <c r="E21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="F21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="I21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.2986</v>
       </c>
       <c r="N21" t="n">
         <v>139</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3941</v>
+        <v>0.5251</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.101</v>
+        <v>-0.1202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8606</v>
+        <v>1.1469</v>
       </c>
       <c r="N22" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3104</v>
+        <v>0.421</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1738</v>
+        <v>-0.223</v>
       </c>
       <c r="E23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="F23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="I23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.678</v>
+        <v>0.9194</v>
       </c>
       <c r="N23" t="n">
         <v>172</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2109</v>
+        <v>0.386</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2604</v>
+        <v>-0.2574</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4606</v>
+        <v>0.843</v>
       </c>
       <c r="N24" t="n">
         <v>139</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0411</v>
+        <v>0.1995</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4082</v>
+        <v>-0.4413</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0897</v>
+        <v>0.4357</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1111</v>
+        <v>0.1055</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5406</v>
+        <v>-0.534</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2427</v>
+        <v>0.2305</v>
       </c>
       <c r="N26" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.171</v>
+        <v>0.0591</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5927</v>
+        <v>-0.5797</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3735</v>
+        <v>0.1291</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3804</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1742</v>
+        <v>-0.004</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5955</v>
+        <v>-0.642</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3804</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6995</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3191</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6995</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3191</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="L28" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2479</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>430</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2313</v>
+        <v>-0.1481</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6452</v>
+        <v>-0.7841</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5052</v>
+        <v>-0.3235</v>
       </c>
       <c r="N29" t="n">
         <v>172</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6026</v>
+        <v>-0.3619</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2759</v>
+        <v>-0.1657</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.8014</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6026</v>
+        <v>-0.3619</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6026</v>
+        <v>-0.4664</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.1045</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6026</v>
+        <v>-0.4664</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6026</v>
+        <v>-0.2425</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1045</v>
       </c>
       <c r="K30" t="n">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6026</v>
+        <v>-0.138</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3484</v>
+        <v>-0.1704</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7471</v>
+        <v>-0.806</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.761</v>
+        <v>-0.3722</v>
       </c>
       <c r="N31" t="n">
         <v>139</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4018</v>
+        <v>-0.1738</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7935</v>
+        <v>-0.8093</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8776</v>
+        <v>-0.3795</v>
       </c>
       <c r="N32" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4222</v>
+        <v>-0.1908</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8113</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9221</v>
+        <v>-0.4167</v>
       </c>
       <c r="N33" t="n">
         <v>172</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4338</v>
+        <v>-0.2279</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8214</v>
+        <v>-0.8627</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9474</v>
+        <v>-0.4978</v>
       </c>
       <c r="N34" t="n">
-        <v>241</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5652</v>
+        <v>-0.3119</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9357</v>
+        <v>-0.9455</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2343</v>
+        <v>-0.6812</v>
       </c>
       <c r="N35" t="n">
         <v>182</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6619</v>
+        <v>-0.3969</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0198</v>
+        <v>-1.0294</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.4455</v>
+        <v>-0.8669</v>
       </c>
       <c r="N36" t="n">
         <v>139</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5167</v>
+        <v>-0.9722</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6945</v>
+        <v>-0.4452</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0482</v>
+        <v>-1.0769</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5167</v>
+        <v>-0.9722</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0388</v>
+        <v>-0.6482</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.4779</v>
+        <v>-0.324</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0388</v>
+        <v>-0.6482</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.842</v>
+        <v>-0.337</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4779</v>
+        <v>-0.324</v>
       </c>
       <c r="K37" t="n">
         <v>242</v>
@@ -2139,7 +2139,7 @@
         <v>63</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3199</v>
+        <v>-0.661</v>
       </c>
       <c r="N37" t="n">
         <v>305</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7724</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1159</v>
+        <v>-1.1494</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6868</v>
+        <v>-1.1327</v>
       </c>
       <c r="N38" t="n">
         <v>172</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7704</v>
+        <v>-1.5204</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8106</v>
+        <v>-0.6962</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1492</v>
+        <v>-1.3244</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7704</v>
+        <v>-1.5204</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0621</v>
+        <v>-1.3123</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.2958</v>
+        <v>-0.1082</v>
       </c>
       <c r="J39" t="n">
-        <v>1.0621</v>
+        <v>-1.3123</v>
       </c>
       <c r="K39" t="n">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="L39" t="n">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2337</v>
+        <v>-1.4205</v>
       </c>
       <c r="N39" t="n">
-        <v>430</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7868</v>
+        <v>-2.1742</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8181</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1558</v>
+        <v>-1.6196</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7868</v>
+        <v>-2.1742</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5857</v>
+        <v>-3.3386</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.2011</v>
+        <v>1.1644</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5857</v>
+        <v>-3.3386</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4747</v>
+        <v>-1.7359</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.2011</v>
+        <v>1.1644</v>
       </c>
       <c r="K40" t="n">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="L40" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6758</v>
+        <v>-0.5714999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>323</v>
+        <v>430</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1017</v>
+        <v>-3.5426</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4202</v>
+        <v>-1.6221</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6796</v>
+        <v>-2.2373</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1017</v>
+        <v>-3.5426</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.0102</v>
+        <v>-3.574</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0915</v>
+        <v>0.0314</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.0102</v>
+        <v>-3.574</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4398</v>
+        <v>-1.8583</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0915</v>
+        <v>0.0314</v>
       </c>
       <c r="K41" t="n">
         <v>242</v>
@@ -2323,7 +2323,7 @@
         <v>63</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5313</v>
+        <v>-1.8269</v>
       </c>
       <c r="N41" t="n">
         <v>305</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.442</v>
+        <v>0.3873</v>
       </c>
       <c r="J2" t="n">
-        <v>11.492</v>
+        <v>10.0698</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2225</v>
+        <v>0.1683</v>
       </c>
       <c r="J3" t="n">
-        <v>5.785</v>
+        <v>4.3758</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.74</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4376</v>
+        <v>-0.2829</v>
       </c>
       <c r="J4" t="n">
-        <v>-11.3776</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4937</v>
+        <v>-0.3213</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.8362</v>
+        <v>-8.3538</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5343</v>
+        <v>-0.3498</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.8918</v>
+        <v>-9.094799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0045</v>
+        <v>0.9212</v>
       </c>
       <c r="J7" t="n">
-        <v>26.117</v>
+        <v>23.9512</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.669</v>
+        <v>0.5947</v>
       </c>
       <c r="J8" t="n">
-        <v>17.394</v>
+        <v>15.4622</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.24</v>
       </c>
       <c r="I9" t="n">
-        <v>0.352</v>
+        <v>0.3258</v>
       </c>
       <c r="J9" t="n">
-        <v>9.151999999999999</v>
+        <v>8.470800000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2133</v>
+        <v>-0.1122</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.5458</v>
+        <v>-2.9172</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5157</v>
+        <v>-0.3306</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.4082</v>
+        <v>-8.595599999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1899</v>
+        <v>1.1358</v>
       </c>
       <c r="J12" t="n">
-        <v>26.1778</v>
+        <v>24.9876</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9792</v>
+        <v>1.006</v>
       </c>
       <c r="J13" t="n">
-        <v>21.5424</v>
+        <v>22.132</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7241</v>
+        <v>0.8096</v>
       </c>
       <c r="J14" t="n">
-        <v>15.9302</v>
+        <v>17.8112</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5554</v>
+        <v>0.651</v>
       </c>
       <c r="J15" t="n">
-        <v>12.2188</v>
+        <v>14.322</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5315</v>
+        <v>0.6274</v>
       </c>
       <c r="J16" t="n">
-        <v>11.693</v>
+        <v>13.8028</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.99</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0353</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7116</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.83</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2214</v>
+        <v>-0.1805</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.8708</v>
+        <v>-3.971</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2549</v>
+        <v>-0.2011</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.6078</v>
+        <v>-4.4242</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.65</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5273</v>
+        <v>-0.3519</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.6006</v>
+        <v>-7.7418</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7012</v>
+        <v>-0.4734</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.4264</v>
+        <v>-10.4148</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0168</v>
+        <v>0.9958</v>
       </c>
       <c r="J22" t="n">
-        <v>35.588</v>
+        <v>34.853</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6222</v>
+        <v>0.6031</v>
       </c>
       <c r="J23" t="n">
-        <v>21.777</v>
+        <v>21.1085</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5703</v>
+        <v>0.5533</v>
       </c>
       <c r="J24" t="n">
-        <v>19.9605</v>
+        <v>19.3655</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3906</v>
+        <v>-0.3225</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.671</v>
+        <v>-11.2875</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5037</v>
+        <v>-0.4387</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.6295</v>
+        <v>-15.3545</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2215</v>
+        <v>0.233</v>
       </c>
       <c r="J27" t="n">
-        <v>7.7525</v>
+        <v>8.154999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.07</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1857</v>
+        <v>0.1903</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4995</v>
+        <v>6.6605</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1271</v>
+        <v>0.1219</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4485</v>
+        <v>4.2665</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1</v>
+        <v>-0.0608</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.5</v>
+        <v>-2.128</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.515</v>
+        <v>-0.333</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.025</v>
+        <v>-11.655</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5457</v>
+        <v>0.5003</v>
       </c>
       <c r="J32" t="n">
-        <v>15.2796</v>
+        <v>14.0084</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3252</v>
+        <v>0.2845</v>
       </c>
       <c r="J33" t="n">
-        <v>9.105600000000001</v>
+        <v>7.966</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1363</v>
+        <v>0.1182</v>
       </c>
       <c r="J34" t="n">
-        <v>3.8164</v>
+        <v>3.3096</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2053</v>
+        <v>-0.116</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.7484</v>
+        <v>-3.248</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5012</v>
+        <v>-0.3216</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.0336</v>
+        <v>-9.004799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7952</v>
+        <v>0.7113</v>
       </c>
       <c r="J37" t="n">
-        <v>22.2656</v>
+        <v>19.9164</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.34</v>
       </c>
       <c r="I38" t="n">
-        <v>0.523</v>
+        <v>0.4532</v>
       </c>
       <c r="J38" t="n">
-        <v>14.644</v>
+        <v>12.6896</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0606</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>1.6968</v>
+        <v>2.3128</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.215</v>
+        <v>-0.1161</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.02</v>
+        <v>-3.2508</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3117</v>
+        <v>-0.1833</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.727600000000001</v>
+        <v>-5.1324</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1899</v>
+        <v>1.117</v>
       </c>
       <c r="J42" t="n">
-        <v>47.596</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6922</v>
       </c>
       <c r="J43" t="n">
-        <v>28.204</v>
+        <v>27.688</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4951</v>
+        <v>0.4965</v>
       </c>
       <c r="J44" t="n">
-        <v>19.804</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.11</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2988</v>
+        <v>0.3428</v>
       </c>
       <c r="J45" t="n">
-        <v>11.952</v>
+        <v>13.712</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8995</v>
+        <v>-0.8628</v>
       </c>
       <c r="J46" t="n">
-        <v>-35.98</v>
+        <v>-34.512</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6388</v>
       </c>
       <c r="J47" t="n">
-        <v>21.552</v>
+        <v>25.552</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0487</v>
+        <v>0.018</v>
       </c>
       <c r="J48" t="n">
-        <v>1.948</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2797</v>
+        <v>-0.1775</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.188</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4881</v>
+        <v>-0.3159</v>
       </c>
       <c r="J50" t="n">
-        <v>-19.524</v>
+        <v>-12.636</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5017</v>
+        <v>-0.3255</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.068</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5457</v>
+        <v>0.471</v>
       </c>
       <c r="J52" t="n">
-        <v>16.371</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4134</v>
+        <v>0.3519</v>
       </c>
       <c r="J53" t="n">
-        <v>12.402</v>
+        <v>10.557</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3994</v>
+        <v>0.3397</v>
       </c>
       <c r="J54" t="n">
-        <v>11.982</v>
+        <v>10.191</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1275</v>
+        <v>0.1325</v>
       </c>
       <c r="J55" t="n">
-        <v>3.825</v>
+        <v>3.975</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5641</v>
+        <v>-0.3673</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.923</v>
+        <v>-11.019</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.36</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6117</v>
+        <v>0.5662</v>
       </c>
       <c r="J57" t="n">
-        <v>18.351</v>
+        <v>16.986</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4689</v>
+        <v>0.4176</v>
       </c>
       <c r="J58" t="n">
-        <v>14.067</v>
+        <v>12.528</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3275</v>
+        <v>-0.2034</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.824999999999999</v>
+        <v>-6.102</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.525</v>
+        <v>-0.3406</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.75</v>
+        <v>-10.218</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5766</v>
+        <v>-0.3782</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.298</v>
+        <v>-11.346</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.714</v>
+        <v>0.8832</v>
       </c>
       <c r="J62" t="n">
-        <v>21.42</v>
+        <v>26.496</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1534</v>
+        <v>0.1748</v>
       </c>
       <c r="J63" t="n">
-        <v>4.602</v>
+        <v>5.244</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0624</v>
+        <v>-0.0245</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.872</v>
+        <v>-0.735</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2577</v>
+        <v>-0.1504</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.731</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3794</v>
+        <v>-0.2342</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.382</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1251</v>
+        <v>1.0713</v>
       </c>
       <c r="J67" t="n">
-        <v>33.753</v>
+        <v>32.139</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7231</v>
+        <v>0.6925</v>
       </c>
       <c r="J68" t="n">
-        <v>21.693</v>
+        <v>20.775</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2324</v>
+        <v>0.2432</v>
       </c>
       <c r="J69" t="n">
-        <v>6.972</v>
+        <v>7.296</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5412</v>
+        <v>-0.4821</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.236</v>
+        <v>-14.463</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7658</v>
+        <v>-0.7192</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.974</v>
+        <v>-21.576</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6737</v>
+        <v>0.8266</v>
       </c>
       <c r="J72" t="n">
-        <v>18.1899</v>
+        <v>22.3182</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.06</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1742</v>
+        <v>0.1729</v>
       </c>
       <c r="J73" t="n">
-        <v>4.7034</v>
+        <v>4.6683</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="J74" t="n">
-        <v>2.4381</v>
+        <v>2.0277</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5635</v>
+        <v>-0.3686</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.2145</v>
+        <v>-9.952199999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6141</v>
+        <v>-0.4059</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.5807</v>
+        <v>-10.9593</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2561</v>
+        <v>1.164</v>
       </c>
       <c r="J77" t="n">
-        <v>33.9147</v>
+        <v>31.428</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>1.176</v>
+        <v>1.113</v>
       </c>
       <c r="J78" t="n">
-        <v>31.752</v>
+        <v>30.051</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.14</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3431</v>
+        <v>0.4085</v>
       </c>
       <c r="J79" t="n">
-        <v>9.2637</v>
+        <v>11.0295</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2304</v>
+        <v>0.2997</v>
       </c>
       <c r="J80" t="n">
-        <v>6.2208</v>
+        <v>8.091900000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6259</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.495</v>
+        <v>-16.8993</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.217</v>
+        <v>0.2065</v>
       </c>
       <c r="J82" t="n">
-        <v>5.425</v>
+        <v>5.1625</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1033</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.5825</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2614</v>
+        <v>-0.1965</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.535</v>
+        <v>-4.9125</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.72</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4401</v>
+        <v>-0.2915</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.0025</v>
+        <v>-7.2875</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7346</v>
+        <v>-0.4974</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.365</v>
+        <v>-12.435</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4577</v>
+        <v>1.0225</v>
       </c>
       <c r="J87" t="n">
-        <v>36.4425</v>
+        <v>25.5625</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2652</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>31.63</v>
+        <v>22.4425</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.37</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9325</v>
+        <v>0.6922</v>
       </c>
       <c r="J89" t="n">
-        <v>23.3125</v>
+        <v>17.305</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2351</v>
+        <v>-0.1532</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.8775</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.0466</v>
+        <v>-1.0275</v>
       </c>
       <c r="J91" t="n">
-        <v>-26.165</v>
+        <v>-25.6875</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5831</v>
+        <v>0.4353</v>
       </c>
       <c r="J92" t="n">
-        <v>17.493</v>
+        <v>13.059</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2624</v>
+        <v>0.2267</v>
       </c>
       <c r="J93" t="n">
-        <v>7.872</v>
+        <v>6.801</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2054</v>
+        <v>0.1878</v>
       </c>
       <c r="J94" t="n">
-        <v>6.162</v>
+        <v>5.634</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.146</v>
+        <v>0.1469</v>
       </c>
       <c r="J95" t="n">
-        <v>4.38</v>
+        <v>4.407</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3209</v>
+        <v>-0.1906</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.627000000000001</v>
+        <v>-5.718</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2356</v>
+        <v>0.1925</v>
       </c>
       <c r="J97" t="n">
-        <v>7.068</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2007</v>
+        <v>0.1605</v>
       </c>
       <c r="J98" t="n">
-        <v>6.021</v>
+        <v>4.815</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1048</v>
+        <v>-0.0614</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.144</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2552</v>
+        <v>-0.1539</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.656</v>
+        <v>-4.617</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.88</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2552</v>
+        <v>-0.1539</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.656</v>
+        <v>-4.617</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4298</v>
+        <v>0.4254</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1748</v>
+        <v>11.0604</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1383</v>
+        <v>-0.1172</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.5958</v>
+        <v>-3.0472</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3936</v>
+        <v>-0.258</v>
       </c>
       <c r="J104" t="n">
-        <v>-10.2336</v>
+        <v>-6.708</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4817</v>
+        <v>-0.3156</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.5242</v>
+        <v>-8.2056</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5772</v>
+        <v>-0.3817</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.0072</v>
+        <v>-9.924200000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.47</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1497</v>
+        <v>0.8237</v>
       </c>
       <c r="J107" t="n">
-        <v>29.8922</v>
+        <v>21.4162</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5606</v>
       </c>
       <c r="J108" t="n">
-        <v>18.3066</v>
+        <v>14.5756</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5592</v>
+        <v>0.493</v>
       </c>
       <c r="J109" t="n">
-        <v>14.5392</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3091</v>
+        <v>0.3607</v>
       </c>
       <c r="J110" t="n">
-        <v>8.0366</v>
+        <v>9.3782</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0057</v>
+        <v>0.0785</v>
       </c>
       <c r="J111" t="n">
-        <v>0.1482</v>
+        <v>2.041</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8187</v>
+        <v>0.6193</v>
       </c>
       <c r="J112" t="n">
-        <v>22.1049</v>
+        <v>16.7211</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6989</v>
+        <v>0.551</v>
       </c>
       <c r="J113" t="n">
-        <v>18.8703</v>
+        <v>14.877</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4101</v>
+        <v>0.4105</v>
       </c>
       <c r="J114" t="n">
-        <v>11.0727</v>
+        <v>11.0835</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3252</v>
+        <v>0.3647</v>
       </c>
       <c r="J115" t="n">
-        <v>8.7804</v>
+        <v>9.8469</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.11</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2682</v>
+        <v>0.3289</v>
       </c>
       <c r="J116" t="n">
-        <v>7.2414</v>
+        <v>8.8803</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.06</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2034</v>
+        <v>0.1964</v>
       </c>
       <c r="J117" t="n">
-        <v>5.4918</v>
+        <v>5.3028</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0613</v>
+        <v>0.0268</v>
       </c>
       <c r="J118" t="n">
-        <v>1.6551</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0613</v>
+        <v>0.0268</v>
       </c>
       <c r="J119" t="n">
-        <v>1.6551</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3168</v>
+        <v>-0.2044</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.553599999999999</v>
+        <v>-5.5188</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7242</v>
+        <v>-0.489</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.5534</v>
+        <v>-13.203</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5568</v>
+        <v>1.0866</v>
       </c>
       <c r="J122" t="n">
-        <v>56.0448</v>
+        <v>39.1176</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7282</v>
+        <v>0.5588</v>
       </c>
       <c r="J123" t="n">
-        <v>26.2152</v>
+        <v>20.1168</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1737</v>
+        <v>0.2279</v>
       </c>
       <c r="J124" t="n">
-        <v>6.2532</v>
+        <v>8.2044</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0001</v>
+        <v>0.061</v>
       </c>
       <c r="J125" t="n">
-        <v>0.0036</v>
+        <v>2.196</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9</v>
+        <v>-0.8633</v>
       </c>
       <c r="J126" t="n">
-        <v>-32.4</v>
+        <v>-31.0788</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7653</v>
+        <v>0.7008</v>
       </c>
       <c r="J127" t="n">
-        <v>27.5508</v>
+        <v>25.2288</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2253</v>
+        <v>0.2358</v>
       </c>
       <c r="J128" t="n">
-        <v>8.110799999999999</v>
+        <v>8.488799999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3742</v>
+        <v>-0.2345</v>
       </c>
       <c r="J129" t="n">
-        <v>-13.4712</v>
+        <v>-8.442</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4454</v>
+        <v>-0.2838</v>
       </c>
       <c r="J130" t="n">
-        <v>-16.0344</v>
+        <v>-10.2168</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5392</v>
+        <v>-0.3508</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.4112</v>
+        <v>-12.6288</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.88</v>
       </c>
       <c r="I132" t="n">
-        <v>1.9484</v>
+        <v>1.6529</v>
       </c>
       <c r="J132" t="n">
-        <v>52.6068</v>
+        <v>44.6283</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6309</v>
+        <v>0.6075</v>
       </c>
       <c r="J133" t="n">
-        <v>17.0343</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6292</v>
+        <v>-0.5715</v>
       </c>
       <c r="J134" t="n">
-        <v>-16.9884</v>
+        <v>-15.4305</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6542</v>
+        <v>-0.598</v>
       </c>
       <c r="J135" t="n">
-        <v>-17.6634</v>
+        <v>-16.146</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.9169</v>
+        <v>-19.6371</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4753</v>
+        <v>0.5589</v>
       </c>
       <c r="J137" t="n">
-        <v>12.8331</v>
+        <v>15.0903</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2875</v>
+        <v>0.3214</v>
       </c>
       <c r="J138" t="n">
-        <v>7.7625</v>
+        <v>8.6778</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2386</v>
+        <v>0.2627</v>
       </c>
       <c r="J139" t="n">
-        <v>6.4422</v>
+        <v>7.0929</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.282</v>
+        <v>-0.1687</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.614</v>
+        <v>-4.5549</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.536</v>
+        <v>-0.3475</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.472</v>
+        <v>-9.3825</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1182</v>
+        <v>1.0725</v>
       </c>
       <c r="J142" t="n">
-        <v>26.8368</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8356</v>
+        <v>0.8275</v>
       </c>
       <c r="J143" t="n">
-        <v>20.0544</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3445</v>
+        <v>0.3923</v>
       </c>
       <c r="J144" t="n">
-        <v>8.268000000000001</v>
+        <v>9.4152</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1681</v>
+        <v>-0.0944</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.0344</v>
+        <v>-2.2656</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.95</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.316</v>
+        <v>-0.2412</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.584</v>
+        <v>-5.7888</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.3</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5461</v>
+        <v>0.6489</v>
       </c>
       <c r="J147" t="n">
-        <v>13.1064</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2171</v>
+        <v>-0.1372</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.2104</v>
+        <v>-3.2928</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.82</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3336</v>
+        <v>-0.21</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.006399999999999</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3336</v>
+        <v>-0.21</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.006399999999999</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3641</v>
+        <v>-0.2301</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.7384</v>
+        <v>-5.5224</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2561</v>
+        <v>-0.2175</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.6098</v>
+        <v>-3.915</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.416</v>
+        <v>-0.3173</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.488</v>
+        <v>-5.7114</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4774</v>
+        <v>-0.3439</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.5932</v>
+        <v>-6.1902</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.549</v>
+        <v>-0.3796</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.882</v>
+        <v>-6.8328</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.53</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6529</v>
+        <v>-0.4446</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.7522</v>
+        <v>-8.002800000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>0.892</v>
+        <v>0.8258</v>
       </c>
       <c r="J157" t="n">
-        <v>16.056</v>
+        <v>14.8644</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7955</v>
+        <v>0.7383</v>
       </c>
       <c r="J158" t="n">
-        <v>14.319</v>
+        <v>13.2894</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.52</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6224</v>
+        <v>0.6015</v>
       </c>
       <c r="J159" t="n">
-        <v>11.2032</v>
+        <v>10.827</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5316</v>
+        <v>0.5311</v>
       </c>
       <c r="J160" t="n">
-        <v>9.5688</v>
+        <v>9.559799999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.24</v>
       </c>
       <c r="I161" t="n">
-        <v>0.271</v>
+        <v>0.2975</v>
       </c>
       <c r="J161" t="n">
-        <v>4.878</v>
+        <v>5.355</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7699</v>
+        <v>0.7409</v>
       </c>
       <c r="J162" t="n">
-        <v>20.7873</v>
+        <v>20.0043</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3419</v>
+        <v>0.3275</v>
       </c>
       <c r="J163" t="n">
-        <v>9.231299999999999</v>
+        <v>8.842499999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.09</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3089</v>
+        <v>0.2996</v>
       </c>
       <c r="J164" t="n">
-        <v>8.340299999999999</v>
+        <v>8.0892</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0653</v>
+        <v>-0.0162</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.7631</v>
+        <v>-0.4374</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3733</v>
+        <v>-0.3109</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.0791</v>
+        <v>-8.394299999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7846</v>
+        <v>0.9759</v>
       </c>
       <c r="J167" t="n">
-        <v>21.1842</v>
+        <v>26.3493</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3959</v>
+        <v>0.4551</v>
       </c>
       <c r="J168" t="n">
-        <v>10.6893</v>
+        <v>12.2877</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3106</v>
+        <v>-0.1886</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.386200000000001</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3559</v>
+        <v>-0.2195</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.609299999999999</v>
+        <v>-5.9265</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.61</v>
+        <v>-0.4023</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.47</v>
+        <v>-10.8621</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.793</v>
+        <v>0.758</v>
       </c>
       <c r="J172" t="n">
-        <v>22.997</v>
+        <v>21.982</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.19</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5808</v>
       </c>
       <c r="J173" t="n">
-        <v>18.0235</v>
+        <v>16.8432</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1661</v>
+        <v>0.1568</v>
       </c>
       <c r="J174" t="n">
-        <v>4.8169</v>
+        <v>4.5472</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2573</v>
+        <v>-0.2062</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.4617</v>
+        <v>-5.9798</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.8093</v>
       </c>
       <c r="J176" t="n">
-        <v>-24.5717</v>
+        <v>-23.4697</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.28</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4655</v>
+        <v>0.5542</v>
       </c>
       <c r="J177" t="n">
-        <v>13.4995</v>
+        <v>16.0718</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3536</v>
+        <v>0.415</v>
       </c>
       <c r="J178" t="n">
-        <v>10.2544</v>
+        <v>12.035</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.19</v>
+        <v>0.2296</v>
       </c>
       <c r="J179" t="n">
-        <v>5.51</v>
+        <v>6.6584</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1633</v>
+        <v>-0.0848</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.7357</v>
+        <v>-2.4592</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2511</v>
+        <v>-0.1437</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.2819</v>
+        <v>-4.1673</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.94</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8511</v>
+        <v>1.5763</v>
       </c>
       <c r="J182" t="n">
-        <v>31.4687</v>
+        <v>26.7971</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.85</v>
       </c>
       <c r="I183" t="n">
-        <v>1.6976</v>
+        <v>1.4775</v>
       </c>
       <c r="J183" t="n">
-        <v>28.8592</v>
+        <v>25.1175</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.61</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2356</v>
+        <v>1.2111</v>
       </c>
       <c r="J184" t="n">
-        <v>21.0052</v>
+        <v>20.5887</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.33</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6448</v>
+        <v>0.7832</v>
       </c>
       <c r="J185" t="n">
-        <v>10.9616</v>
+        <v>13.3144</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.3</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5812</v>
+        <v>0.7156</v>
       </c>
       <c r="J186" t="n">
-        <v>9.8804</v>
+        <v>12.1652</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0834</v>
+        <v>0.0619</v>
       </c>
       <c r="J187" t="n">
-        <v>1.4178</v>
+        <v>1.0523</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.531</v>
+        <v>-0.401</v>
       </c>
       <c r="J188" t="n">
-        <v>-9.026999999999999</v>
+        <v>-6.817</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.5</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.4539</v>
       </c>
       <c r="J189" t="n">
-        <v>-11.0449</v>
+        <v>-7.7163</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.7829</v>
+        <v>-0.5393</v>
       </c>
       <c r="J190" t="n">
-        <v>-13.3093</v>
+        <v>-9.168100000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.31</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9162</v>
+        <v>-0.637</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.5754</v>
+        <v>-10.829</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.91</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8347</v>
+        <v>1.5592</v>
       </c>
       <c r="J192" t="n">
-        <v>36.694</v>
+        <v>31.184</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.71</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4811</v>
+        <v>1.3337</v>
       </c>
       <c r="J193" t="n">
-        <v>29.622</v>
+        <v>26.674</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.2282</v>
+        <v>1.1845</v>
       </c>
       <c r="J194" t="n">
-        <v>24.564</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.37</v>
       </c>
       <c r="I195" t="n">
-        <v>0.757</v>
+        <v>0.888</v>
       </c>
       <c r="J195" t="n">
-        <v>15.14</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1092</v>
+        <v>-0.0227</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.184</v>
+        <v>-0.454</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.96</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1091</v>
+        <v>0.0922</v>
       </c>
       <c r="J197" t="n">
-        <v>2.182</v>
+        <v>1.844</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.63</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.4297</v>
+        <v>-0.3398</v>
       </c>
       <c r="J198" t="n">
-        <v>-8.593999999999999</v>
+        <v>-6.796</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.6151</v>
+        <v>-0.4305</v>
       </c>
       <c r="J199" t="n">
-        <v>-12.302</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.37</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.8441</v>
+        <v>-0.5825</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.882</v>
+        <v>-11.65</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8832</v>
+        <v>-0.6116</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.664</v>
+        <v>-12.232</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0205</v>
+        <v>-0.0461</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.4715</v>
+        <v>-1.0603</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.86</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1819</v>
+        <v>-0.1525</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.1837</v>
+        <v>-3.5075</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2503</v>
+        <v>-0.1942</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.7569</v>
+        <v>-4.4666</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4776</v>
+        <v>-0.3174</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.9848</v>
+        <v>-7.3002</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6162</v>
+        <v>-0.4114</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.1726</v>
+        <v>-9.462199999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.69</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8699</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>20.0077</v>
+        <v>18.2344</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6706</v>
+        <v>0.6076</v>
       </c>
       <c r="J208" t="n">
-        <v>15.4238</v>
+        <v>13.9748</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.39</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5212</v>
+        <v>0.4811</v>
       </c>
       <c r="J209" t="n">
-        <v>11.9876</v>
+        <v>11.0653</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.21</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2625</v>
+        <v>0.2786</v>
       </c>
       <c r="J210" t="n">
-        <v>6.0375</v>
+        <v>6.4078</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1548</v>
+        <v>-0.0698</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.5604</v>
+        <v>-1.6054</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.29</v>
       </c>
       <c r="I212" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J212" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>2.14</v>
       </c>
       <c r="I213" t="n">
-        <v>2.057</v>
+        <v>1.7827</v>
       </c>
       <c r="J213" t="n">
-        <v>37.026</v>
+        <v>32.0886</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.52</v>
       </c>
       <c r="I214" t="n">
-        <v>1.015</v>
+        <v>1.1038</v>
       </c>
       <c r="J214" t="n">
-        <v>18.27</v>
+        <v>19.8684</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5049</v>
+        <v>0.6372</v>
       </c>
       <c r="J215" t="n">
-        <v>9.088200000000001</v>
+        <v>11.4696</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0035</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.063</v>
+        <v>1.6002</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2251</v>
+        <v>-0.2012</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.0518</v>
+        <v>-3.6216</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.59</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4391</v>
+        <v>-0.3564</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.9038</v>
+        <v>-6.4152</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4864</v>
+        <v>-0.3871</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.7552</v>
+        <v>-6.9678</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.31</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.9006</v>
+        <v>-0.6257</v>
       </c>
       <c r="J220" t="n">
-        <v>-16.2108</v>
+        <v>-11.2626</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.25</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.6866</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.6454</v>
+        <v>-12.3588</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8685</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>20.844</v>
+        <v>21.3264</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8219</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>19.7256</v>
+        <v>20.2632</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.31</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J224" t="n">
-        <v>18.5688</v>
+        <v>19.1976</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.696</v>
+        <v>0.7331</v>
       </c>
       <c r="J225" t="n">
-        <v>16.704</v>
+        <v>17.5944</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1196</v>
+        <v>0.1986</v>
       </c>
       <c r="J226" t="n">
-        <v>2.8704</v>
+        <v>4.7664</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.21</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4617</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J227" t="n">
-        <v>11.0808</v>
+        <v>12.7872</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2602</v>
+        <v>0.2636</v>
       </c>
       <c r="J228" t="n">
-        <v>6.2448</v>
+        <v>6.3264</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2886</v>
+        <v>-0.1988</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.9264</v>
+        <v>-4.7712</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5484</v>
+        <v>-0.3618</v>
       </c>
       <c r="J230" t="n">
-        <v>-13.1616</v>
+        <v>-8.683199999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8808</v>
+        <v>-0.61</v>
       </c>
       <c r="J231" t="n">
-        <v>-21.1392</v>
+        <v>-14.64</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3847</v>
+        <v>1.2481</v>
       </c>
       <c r="J232" t="n">
-        <v>37.3869</v>
+        <v>33.6987</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.33</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8456</v>
+        <v>0.8542</v>
       </c>
       <c r="J233" t="n">
-        <v>22.8312</v>
+        <v>23.0634</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.32</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8224</v>
+        <v>0.8316</v>
       </c>
       <c r="J234" t="n">
-        <v>22.2048</v>
+        <v>22.4532</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1333</v>
+        <v>-0.0556</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.5991</v>
+        <v>-1.5012</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4842</v>
+        <v>-0.4104</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.0734</v>
+        <v>-11.0808</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3625</v>
+        <v>0.4045</v>
       </c>
       <c r="J237" t="n">
-        <v>9.7875</v>
+        <v>10.9215</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1846</v>
+        <v>-0.1164</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.9842</v>
+        <v>-3.1428</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2035</v>
+        <v>-0.1274</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.4945</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2035</v>
+        <v>-0.1274</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.4945</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.367</v>
+        <v>-0.2313</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.909000000000001</v>
+        <v>-6.2451</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.63</v>
       </c>
       <c r="I242" t="n">
-        <v>1.5153</v>
+        <v>1.3321</v>
       </c>
       <c r="J242" t="n">
-        <v>42.4284</v>
+        <v>37.2988</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7683</v>
+        <v>0.7487</v>
       </c>
       <c r="J243" t="n">
-        <v>21.5124</v>
+        <v>20.9636</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0888</v>
+        <v>-0.0276</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.4864</v>
+        <v>-0.7728</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.85</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5836</v>
+        <v>-0.5221</v>
       </c>
       <c r="J245" t="n">
-        <v>-16.3408</v>
+        <v>-14.6188</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6091</v>
+        <v>-0.5491</v>
       </c>
       <c r="J246" t="n">
-        <v>-17.0548</v>
+        <v>-15.3748</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.627</v>
+        <v>0.7625</v>
       </c>
       <c r="J247" t="n">
-        <v>17.556</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3324</v>
+        <v>0.3771</v>
       </c>
       <c r="J248" t="n">
-        <v>9.3072</v>
+        <v>10.5588</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.95</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.143</v>
+        <v>-0.0779</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.004</v>
+        <v>-2.1812</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3881</v>
+        <v>-0.2413</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.8668</v>
+        <v>-6.7564</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4023</v>
+        <v>-0.2513</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.2644</v>
+        <v>-7.0364</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>1.017</v>
+        <v>1.0188</v>
       </c>
       <c r="J252" t="n">
-        <v>22.374</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>1.017</v>
+        <v>1.0188</v>
       </c>
       <c r="J253" t="n">
-        <v>22.374</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8858</v>
       </c>
       <c r="J254" t="n">
-        <v>18.9508</v>
+        <v>19.4876</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.19</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4404</v>
+        <v>0.5212</v>
       </c>
       <c r="J255" t="n">
-        <v>9.688800000000001</v>
+        <v>11.4664</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.02</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0506</v>
+        <v>0.0279</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.1132</v>
+        <v>0.6138</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2537</v>
+        <v>0.2564</v>
       </c>
       <c r="J257" t="n">
-        <v>5.5814</v>
+        <v>5.6408</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.96</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0274</v>
+        <v>-0.0453</v>
       </c>
       <c r="J258" t="n">
-        <v>-0.6028</v>
+        <v>-0.9966</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1788</v>
+        <v>-0.1402</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.9336</v>
+        <v>-3.0844</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4267</v>
+        <v>-0.2784</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.3874</v>
+        <v>-6.1248</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6688</v>
+        <v>-0.4479</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.7136</v>
+        <v>-9.8538</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8244</v>
+        <v>0.7948</v>
       </c>
       <c r="J262" t="n">
-        <v>23.9076</v>
+        <v>23.0492</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2563</v>
+        <v>0.224</v>
       </c>
       <c r="J263" t="n">
-        <v>7.4327</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0311</v>
+        <v>-0.0045</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.9019</v>
+        <v>-0.1305</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3377</v>
+        <v>-0.2047</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.7933</v>
+        <v>-5.9363</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4776</v>
+        <v>-0.3042</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.8504</v>
+        <v>-8.8218</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.31</v>
+        <v>0.2515</v>
       </c>
       <c r="J267" t="n">
-        <v>8.99</v>
+        <v>7.2935</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1756</v>
+        <v>0.1401</v>
       </c>
       <c r="J268" t="n">
-        <v>5.0924</v>
+        <v>4.0629</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0376</v>
+        <v>0.0436</v>
       </c>
       <c r="J269" t="n">
-        <v>1.0904</v>
+        <v>1.2644</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0857</v>
+        <v>-0.0396</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.4853</v>
+        <v>-1.1484</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1298</v>
+        <v>-0.0672</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.7642</v>
+        <v>-1.9488</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7395</v>
+        <v>0.7038</v>
       </c>
       <c r="J272" t="n">
-        <v>21.4455</v>
+        <v>20.4102</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.04</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1469</v>
+        <v>0.1556</v>
       </c>
       <c r="J273" t="n">
-        <v>4.2601</v>
+        <v>4.5124</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.02</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0619</v>
+        <v>0.0859</v>
       </c>
       <c r="J274" t="n">
-        <v>1.7951</v>
+        <v>2.4911</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.016</v>
+        <v>0.0455</v>
       </c>
       <c r="J275" t="n">
-        <v>0.464</v>
+        <v>1.3195</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3894</v>
+        <v>-0.3323</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.2926</v>
+        <v>-9.636699999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5206</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>15.0974</v>
+        <v>17.9945</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2794</v>
+        <v>0.3159</v>
       </c>
       <c r="J278" t="n">
-        <v>8.102600000000001</v>
+        <v>9.161099999999999</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2127</v>
+        <v>0.2378</v>
       </c>
       <c r="J279" t="n">
-        <v>6.1683</v>
+        <v>6.8962</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3485</v>
+        <v>-0.213</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.1065</v>
+        <v>-6.177</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3777</v>
+        <v>-0.2333</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.9533</v>
+        <v>-6.7657</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2222</v>
+        <v>0.1787</v>
       </c>
       <c r="J282" t="n">
-        <v>6.666</v>
+        <v>5.361</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0211</v>
+        <v>0.0032</v>
       </c>
       <c r="J283" t="n">
-        <v>0.633</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.99</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0153</v>
+        <v>-0.0186</v>
       </c>
       <c r="J284" t="n">
-        <v>-0.459</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.97</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0716</v>
+        <v>-0.0478</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.148</v>
+        <v>-1.434</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3763</v>
+        <v>-0.2355</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.289</v>
+        <v>-7.065</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7462</v>
+        <v>0.6625</v>
       </c>
       <c r="J287" t="n">
-        <v>22.386</v>
+        <v>19.875</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2407</v>
+        <v>0.213</v>
       </c>
       <c r="J288" t="n">
-        <v>7.221</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.221</v>
+        <v>0.2002</v>
       </c>
       <c r="J289" t="n">
-        <v>6.63</v>
+        <v>6.006</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0538</v>
+        <v>-0.0116</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.614</v>
+        <v>-0.348</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3372</v>
+        <v>-0.2019</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.116</v>
+        <v>-6.057</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2153</v>
+        <v>1.133</v>
       </c>
       <c r="J292" t="n">
-        <v>32.8131</v>
+        <v>30.591</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.7352</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J293" t="n">
-        <v>19.8504</v>
+        <v>19.4211</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3721</v>
+        <v>0.3975</v>
       </c>
       <c r="J294" t="n">
-        <v>10.0467</v>
+        <v>10.7325</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3367</v>
+        <v>-0.2656</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.0909</v>
+        <v>-7.1712</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.86</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5628</v>
+        <v>-0.4991</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.1956</v>
+        <v>-13.4757</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.23</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4471</v>
+        <v>0.5158</v>
       </c>
       <c r="J297" t="n">
-        <v>12.0717</v>
+        <v>13.9266</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0001</v>
+        <v>-0.0154</v>
       </c>
       <c r="J298" t="n">
-        <v>0.0027</v>
+        <v>-0.4158</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0958</v>
+        <v>-0.0711</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.5866</v>
+        <v>-1.9197</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.258</v>
+        <v>-0.16</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.966</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.66</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5608</v>
+        <v>-0.367</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.1416</v>
+        <v>-9.909000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.57</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3559</v>
+        <v>1.2283</v>
       </c>
       <c r="J302" t="n">
-        <v>36.6093</v>
+        <v>33.1641</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.35</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9021</v>
+        <v>0.9048</v>
       </c>
       <c r="J303" t="n">
-        <v>24.3567</v>
+        <v>24.4296</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4565</v>
+        <v>0.511</v>
       </c>
       <c r="J304" t="n">
-        <v>12.3255</v>
+        <v>13.797</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.0801</v>
+        <v>0.1503</v>
       </c>
       <c r="J305" t="n">
-        <v>2.1627</v>
+        <v>4.0581</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5058</v>
+        <v>-0.4342</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.6566</v>
+        <v>-11.7234</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5612</v>
+        <v>0.6704</v>
       </c>
       <c r="J307" t="n">
-        <v>15.1524</v>
+        <v>18.1008</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2447</v>
+        <v>0.2585</v>
       </c>
       <c r="J308" t="n">
-        <v>6.6069</v>
+        <v>6.9795</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2122</v>
+        <v>-0.1294</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.7294</v>
+        <v>-3.4938</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2801</v>
+        <v>-0.1724</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.5627</v>
+        <v>-4.6548</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6392</v>
+        <v>-0.4245</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.2584</v>
+        <v>-11.4615</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.27</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4208</v>
+        <v>0.3668</v>
       </c>
       <c r="J312" t="n">
-        <v>14.728</v>
+        <v>12.838</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3925</v>
+        <v>0.3431</v>
       </c>
       <c r="J313" t="n">
-        <v>13.7375</v>
+        <v>12.0085</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1918</v>
+        <v>0.1956</v>
       </c>
       <c r="J314" t="n">
-        <v>6.713</v>
+        <v>6.846</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1918</v>
+        <v>0.1956</v>
       </c>
       <c r="J315" t="n">
-        <v>6.713</v>
+        <v>6.846</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.12</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1752</v>
+        <v>0.1822</v>
       </c>
       <c r="J316" t="n">
-        <v>6.132</v>
+        <v>6.377</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3033</v>
+        <v>0.2477</v>
       </c>
       <c r="J317" t="n">
-        <v>10.6155</v>
+        <v>8.669499999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.058</v>
+        <v>0.0186</v>
       </c>
       <c r="J318" t="n">
-        <v>2.03</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0677</v>
+        <v>-0.0653</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.3695</v>
+        <v>-2.2855</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4547</v>
+        <v>-0.2939</v>
       </c>
       <c r="J320" t="n">
-        <v>-15.9145</v>
+        <v>-10.2865</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.3793</v>
       </c>
       <c r="J321" t="n">
-        <v>-20.1635</v>
+        <v>-13.2755</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4201</v>
+        <v>0.4759</v>
       </c>
       <c r="J322" t="n">
-        <v>10.5025</v>
+        <v>11.8975</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.83</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2602</v>
+        <v>-0.1891</v>
       </c>
       <c r="J323" t="n">
-        <v>-6.505</v>
+        <v>-4.7275</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3049</v>
+        <v>-0.2081</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.6225</v>
+        <v>-5.2025</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4343</v>
+        <v>-0.2853</v>
       </c>
       <c r="J325" t="n">
-        <v>-10.8575</v>
+        <v>-7.1325</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.57</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6521</v>
+        <v>-0.436</v>
       </c>
       <c r="J326" t="n">
-        <v>-16.3025</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.72</v>
       </c>
       <c r="I327" t="n">
-        <v>1.5546</v>
+        <v>1.3683</v>
       </c>
       <c r="J327" t="n">
-        <v>38.865</v>
+        <v>34.2075</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1918</v>
+        <v>1.1421</v>
       </c>
       <c r="J328" t="n">
-        <v>29.795</v>
+        <v>28.5525</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.52</v>
       </c>
       <c r="I329" t="n">
-        <v>1.1715</v>
+        <v>1.13</v>
       </c>
       <c r="J329" t="n">
-        <v>29.2875</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.35</v>
       </c>
       <c r="I330" t="n">
-        <v>0.7725</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J330" t="n">
-        <v>19.3125</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7216</v>
+        <v>-0.6635</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.04</v>
+        <v>-16.5875</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.18</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3509</v>
+        <v>0.3987</v>
       </c>
       <c r="J332" t="n">
-        <v>14.7378</v>
+        <v>16.7454</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.09</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2065</v>
+        <v>0.2235</v>
       </c>
       <c r="J333" t="n">
-        <v>8.673</v>
+        <v>9.387</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.06</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1509</v>
+        <v>0.1597</v>
       </c>
       <c r="J334" t="n">
-        <v>6.3378</v>
+        <v>6.7074</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I335" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="J335" t="n">
-        <v>3.6498</v>
+        <v>3.7884</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.535</v>
+        <v>-0.3468</v>
       </c>
       <c r="J336" t="n">
-        <v>-22.47</v>
+        <v>-14.5656</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.57</v>
       </c>
       <c r="I337" t="n">
-        <v>1.4148</v>
+        <v>1.2639</v>
       </c>
       <c r="J337" t="n">
-        <v>59.4216</v>
+        <v>53.0838</v>
       </c>
     </row>
     <row r="338">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2103</v>
+        <v>0.2399</v>
       </c>
       <c r="J339" t="n">
-        <v>8.832599999999999</v>
+        <v>10.0758</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.89</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4674</v>
+        <v>-0.4038</v>
       </c>
       <c r="J340" t="n">
-        <v>-19.6308</v>
+        <v>-16.9596</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6259</v>
+        <v>-0.5688</v>
       </c>
       <c r="J341" t="n">
-        <v>-26.2878</v>
+        <v>-23.8896</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.26</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4665</v>
+        <v>0.5462</v>
       </c>
       <c r="J342" t="n">
-        <v>13.5285</v>
+        <v>15.8398</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.03</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0912</v>
+        <v>0.0915</v>
       </c>
       <c r="J343" t="n">
-        <v>2.6448</v>
+        <v>2.6535</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.99</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0417</v>
+        <v>-0.0207</v>
       </c>
       <c r="J344" t="n">
-        <v>-1.2093</v>
+        <v>-0.6002999999999999</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2619</v>
+        <v>-0.1564</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.5951</v>
+        <v>-4.5356</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3096</v>
+        <v>-0.1882</v>
       </c>
       <c r="J346" t="n">
-        <v>-8.978400000000001</v>
+        <v>-5.4578</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7126</v>
+        <v>0.6858</v>
       </c>
       <c r="J347" t="n">
-        <v>20.6654</v>
+        <v>19.8882</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.534</v>
+        <v>0.5099</v>
       </c>
       <c r="J348" t="n">
-        <v>15.486</v>
+        <v>14.7871</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.17</v>
       </c>
       <c r="I349" t="n">
-        <v>0.534</v>
+        <v>0.5099</v>
       </c>
       <c r="J349" t="n">
-        <v>15.486</v>
+        <v>14.7871</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1775</v>
+        <v>-0.1161</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.1475</v>
+        <v>-3.3669</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4666</v>
+        <v>-0.4032</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.5314</v>
+        <v>-11.6928</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.92</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.0333</v>
+        <v>-0.0593</v>
       </c>
       <c r="J352" t="n">
-        <v>-0.666</v>
+        <v>-1.186</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.91</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0511</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.022</v>
+        <v>-1.438</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.7</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.3981</v>
+        <v>-0.2963</v>
       </c>
       <c r="J354" t="n">
-        <v>-7.962</v>
+        <v>-5.926</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.55</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.6418</v>
+        <v>-0.434</v>
       </c>
       <c r="J355" t="n">
-        <v>-12.836</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.36</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.8839</v>
+        <v>-0.6118</v>
       </c>
       <c r="J356" t="n">
-        <v>-17.678</v>
+        <v>-12.236</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.5745</v>
+        <v>1.3809</v>
       </c>
       <c r="J357" t="n">
-        <v>31.49</v>
+        <v>27.618</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.66</v>
       </c>
       <c r="I358" t="n">
-        <v>1.4458</v>
+        <v>1.2983</v>
       </c>
       <c r="J358" t="n">
-        <v>28.916</v>
+        <v>25.966</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.3</v>
       </c>
       <c r="I359" t="n">
-        <v>0.6574</v>
+        <v>0.7591</v>
       </c>
       <c r="J359" t="n">
-        <v>13.148</v>
+        <v>15.182</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.26</v>
       </c>
       <c r="I360" t="n">
-        <v>0.5642</v>
+        <v>0.6674</v>
       </c>
       <c r="J360" t="n">
-        <v>11.284</v>
+        <v>13.348</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3124</v>
+        <v>-0.2247</v>
       </c>
       <c r="J361" t="n">
-        <v>-6.248</v>
+        <v>-4.494</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.76</v>
       </c>
       <c r="I362" t="n">
-        <v>1.6242</v>
+        <v>1.4138</v>
       </c>
       <c r="J362" t="n">
-        <v>34.1082</v>
+        <v>29.6898</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.73</v>
       </c>
       <c r="I363" t="n">
-        <v>1.5702</v>
+        <v>1.3788</v>
       </c>
       <c r="J363" t="n">
-        <v>32.9742</v>
+        <v>28.9548</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.37</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8168</v>
+        <v>0.9097</v>
       </c>
       <c r="J364" t="n">
-        <v>17.1528</v>
+        <v>19.1037</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.21</v>
       </c>
       <c r="I365" t="n">
-        <v>0.4425</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="J365" t="n">
-        <v>9.2925</v>
+        <v>11.4639</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.9</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5233</v>
+        <v>-0.4471</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.9893</v>
+        <v>-9.389099999999999</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>0.93</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.0199</v>
+        <v>-0.0496</v>
       </c>
       <c r="J367" t="n">
-        <v>-0.4179</v>
+        <v>-1.0416</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.91</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0559</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.1739</v>
+        <v>-1.5729</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.63</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.5315</v>
+        <v>-0.3609</v>
       </c>
       <c r="J369" t="n">
-        <v>-11.1615</v>
+        <v>-7.5789</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.53</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.672</v>
+        <v>-0.4544</v>
       </c>
       <c r="J370" t="n">
-        <v>-14.112</v>
+        <v>-9.542400000000001</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.49</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7244</v>
+        <v>-0.4918</v>
       </c>
       <c r="J371" t="n">
-        <v>-15.2124</v>
+        <v>-10.3278</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.78</v>
       </c>
       <c r="I372" t="n">
-        <v>1.6675</v>
+        <v>1.4412</v>
       </c>
       <c r="J372" t="n">
-        <v>38.3525</v>
+        <v>33.1476</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.63</v>
       </c>
       <c r="I373" t="n">
-        <v>1.3928</v>
+        <v>1.2642</v>
       </c>
       <c r="J373" t="n">
-        <v>32.0344</v>
+        <v>29.0766</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.27</v>
       </c>
       <c r="I374" t="n">
-        <v>0.5911</v>
+        <v>0.6923</v>
       </c>
       <c r="J374" t="n">
-        <v>13.5953</v>
+        <v>15.9229</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2239</v>
+        <v>0.3177</v>
       </c>
       <c r="J375" t="n">
-        <v>5.1497</v>
+        <v>7.3071</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I376" t="n">
-        <v>0.1144</v>
+        <v>0.2039</v>
       </c>
       <c r="J376" t="n">
-        <v>2.6312</v>
+        <v>4.6897</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.01</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1733</v>
+        <v>0.1508</v>
       </c>
       <c r="J377" t="n">
-        <v>3.9859</v>
+        <v>3.4684</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.83</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.192</v>
+        <v>-0.1686</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.416</v>
+        <v>-3.8778</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.6</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.577</v>
+        <v>-0.3895</v>
       </c>
       <c r="J379" t="n">
-        <v>-13.271</v>
+        <v>-8.958500000000001</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.58</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.6052</v>
+        <v>-0.4082</v>
       </c>
       <c r="J380" t="n">
-        <v>-13.9196</v>
+        <v>-9.3886</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.49</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7255</v>
+        <v>-0.4924</v>
       </c>
       <c r="J381" t="n">
-        <v>-16.6865</v>
+        <v>-11.3252</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3133/event_3133_evp_summary.xlsx
+++ b/database/event/3133/event_3133_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.717499999999999</v>
+        <v>8.770300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9916</v>
+        <v>4.0158</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2975</v>
+        <v>3.3682</v>
       </c>
       <c r="E2" t="n">
-        <v>8.717499999999999</v>
+        <v>8.770300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9369</v>
+        <v>3.9516</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7806</v>
+        <v>4.8187</v>
       </c>
       <c r="H2" t="n">
-        <v>8.385</v>
+        <v>8.143599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3598</v>
+        <v>4.3975</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7806</v>
+        <v>4.8187</v>
       </c>
       <c r="K2" t="n">
         <v>109</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>9.1404</v>
+        <v>9.216200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3584</v>
+        <v>6.4125</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9114</v>
+        <v>2.9362</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2325</v>
+        <v>2.2949</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3584</v>
+        <v>6.4125</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0138</v>
+        <v>3.9436</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3446</v>
+        <v>2.4689</v>
       </c>
       <c r="H3" t="n">
-        <v>8.655799999999999</v>
+        <v>8.1173</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5006</v>
+        <v>4.3833</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3446</v>
+        <v>2.4689</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8452</v>
+        <v>6.8522</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3504</v>
+        <v>6.2509</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9077</v>
+        <v>2.8622</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2289</v>
+        <v>2.2213</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3504</v>
+        <v>6.2509</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9161</v>
+        <v>3.8671</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4343</v>
+        <v>2.3838</v>
       </c>
       <c r="H4" t="n">
-        <v>8.3117</v>
+        <v>7.8648</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3217</v>
+        <v>4.2469</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4343</v>
+        <v>2.3838</v>
       </c>
       <c r="K4" t="n">
         <v>109</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>6.756</v>
+        <v>6.6307</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6356</v>
+        <v>5.4899</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5804</v>
+        <v>2.5137</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9062</v>
+        <v>1.8749</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6356</v>
+        <v>5.4899</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8867</v>
+        <v>2.7926</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7489</v>
+        <v>2.6973</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6846</v>
+        <v>4.3197</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4358</v>
+        <v>2.3326</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7489</v>
+        <v>2.6973</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>5.184699999999999</v>
+        <v>5.0299</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1775</v>
+        <v>4.2246</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9128</v>
+        <v>1.9344</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2479</v>
+        <v>1.2989</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1775</v>
+        <v>4.2246</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1103</v>
+        <v>3.0755</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0672</v>
+        <v>1.1491</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4725</v>
+        <v>5.253</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8454</v>
+        <v>2.8366</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0672</v>
+        <v>1.1491</v>
       </c>
       <c r="K6" t="n">
         <v>173</v>
@@ -713,7 +713,7 @@
         <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9126</v>
+        <v>3.9857</v>
       </c>
       <c r="N6" t="n">
         <v>254</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6962</v>
+        <v>3.6423</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6924</v>
+        <v>1.6677</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0306</v>
+        <v>1.0338</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6962</v>
+        <v>3.6423</v>
       </c>
       <c r="F7" t="n">
-        <v>4.019</v>
+        <v>3.9837</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3228</v>
+        <v>-0.3414</v>
       </c>
       <c r="H7" t="n">
-        <v>8.673999999999999</v>
+        <v>8.2494</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5101</v>
+        <v>4.4546</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3228</v>
+        <v>-0.3414</v>
       </c>
       <c r="K7" t="n">
         <v>173</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1873</v>
+        <v>4.1132</v>
       </c>
       <c r="N7" t="n">
         <v>254</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6518</v>
+        <v>3.551</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6721</v>
+        <v>1.6259</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0106</v>
+        <v>0.9923</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6518</v>
+        <v>3.551</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5355</v>
+        <v>3.6531</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1163</v>
+        <v>-0.1021</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5355</v>
+        <v>7.1587</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7984</v>
+        <v>3.8657</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1163</v>
+        <v>-0.1021</v>
       </c>
       <c r="K8" t="n">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="L8" t="n">
-        <v>232</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9147</v>
+        <v>3.7636</v>
       </c>
       <c r="N8" t="n">
-        <v>430</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6478</v>
+        <v>3.5426</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6703</v>
+        <v>1.6221</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0088</v>
+        <v>0.9885</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6478</v>
+        <v>3.5426</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7352</v>
+        <v>1.2534</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>2.2892</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6742</v>
+        <v>1.2534</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9902</v>
+        <v>0.6768</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>2.2892</v>
       </c>
       <c r="K9" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9028</v>
+        <v>2.966</v>
       </c>
       <c r="N9" t="n">
-        <v>305</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6179</v>
+        <v>3.5418</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6566</v>
+        <v>1.6217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9953</v>
+        <v>0.9881</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6179</v>
+        <v>3.5418</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6179</v>
+        <v>2.3639</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.1779</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5845</v>
+        <v>2.905</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5845</v>
+        <v>1.5687</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.1779</v>
       </c>
       <c r="K10" t="n">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5845</v>
+        <v>2.7466</v>
       </c>
       <c r="N10" t="n">
-        <v>241</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5618</v>
+        <v>3.2676</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6309</v>
+        <v>1.4962</v>
       </c>
       <c r="D11" t="n">
-        <v>0.97</v>
+        <v>0.8633</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5618</v>
+        <v>3.2676</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5016</v>
+        <v>3.2676</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0602</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3278</v>
+        <v>4.4269</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7303</v>
+        <v>4.4269</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0602</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="L11" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7905</v>
+        <v>4.4269</v>
       </c>
       <c r="N11" t="n">
-        <v>430</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3165</v>
+        <v>3.2537</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5186</v>
+        <v>1.4898</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8592</v>
+        <v>0.8569</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3165</v>
+        <v>3.2537</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7069</v>
+        <v>3.66</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3904</v>
+        <v>-0.4063</v>
       </c>
       <c r="H12" t="n">
-        <v>7.5745</v>
+        <v>7.1816</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9384</v>
+        <v>3.878</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3904</v>
+        <v>-0.4063</v>
       </c>
       <c r="K12" t="n">
         <v>173</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>3.548</v>
+        <v>3.4717</v>
       </c>
       <c r="N12" t="n">
         <v>254</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2815</v>
+        <v>3.0421</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5025</v>
+        <v>1.3929</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8434</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2815</v>
+        <v>3.0421</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2815</v>
+        <v>2.7593</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8459</v>
+        <v>4.2096</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8459</v>
+        <v>2.2732</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="K13" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8459</v>
+        <v>2.556</v>
       </c>
       <c r="N13" t="n">
-        <v>241</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0852</v>
+        <v>2.9616</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4127</v>
+        <v>1.3561</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7548</v>
+        <v>0.724</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0852</v>
+        <v>2.9616</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8734</v>
+        <v>2.9616</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2118</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6379</v>
+        <v>3.7571</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4115</v>
+        <v>3.7571</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2118</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L14" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6233</v>
+        <v>3.7571</v>
       </c>
       <c r="N14" t="n">
-        <v>305</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.741</v>
+        <v>2.6386</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2551</v>
+        <v>1.2082</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5994</v>
+        <v>0.5769</v>
       </c>
       <c r="E15" t="n">
-        <v>2.741</v>
+        <v>2.6386</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3468</v>
+        <v>3.2887</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6058</v>
+        <v>-0.6501</v>
       </c>
       <c r="H15" t="n">
-        <v>6.3057</v>
+        <v>5.9566</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2787</v>
+        <v>3.2165</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6058</v>
+        <v>-0.6501</v>
       </c>
       <c r="K15" t="n">
         <v>173</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6729</v>
+        <v>2.5664</v>
       </c>
       <c r="N15" t="n">
         <v>254</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7137</v>
+        <v>2.5569</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2426</v>
+        <v>1.1708</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5871</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7137</v>
+        <v>2.5569</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1929</v>
+        <v>3.0339</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5208</v>
+        <v>-0.477</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>5.1157</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1647</v>
+        <v>2.7625</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5208</v>
+        <v>-0.477</v>
       </c>
       <c r="K16" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="L16" t="n">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6855</v>
+        <v>2.2855</v>
       </c>
       <c r="N16" t="n">
-        <v>430</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6256</v>
+        <v>2.498</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2022</v>
+        <v>1.1438</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5473</v>
+        <v>0.5129</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6256</v>
+        <v>2.498</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0933</v>
+        <v>1.9145</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4677</v>
+        <v>0.5835</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4127</v>
+        <v>1.9145</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8144</v>
+        <v>1.0338</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4677</v>
+        <v>0.5835</v>
       </c>
       <c r="K17" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="L17" t="n">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3467</v>
+        <v>1.6173</v>
       </c>
       <c r="N17" t="n">
-        <v>254</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0597</v>
+        <v>1.9569</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9431</v>
+        <v>0.896</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2918</v>
+        <v>0.2666</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0597</v>
+        <v>1.9569</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2674</v>
+        <v>2.1865</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2077</v>
+        <v>-0.2296</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5027</v>
+        <v>2.3199</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3013</v>
+        <v>1.2528</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2077</v>
+        <v>-0.2296</v>
       </c>
       <c r="K18" t="n">
         <v>242</v>
@@ -1265,7 +1265,7 @@
         <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0936</v>
+        <v>1.0232</v>
       </c>
       <c r="N18" t="n">
         <v>305</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="C19" t="n">
-        <v>0.673</v>
+        <v>0.6506</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0256</v>
+        <v>0.0226</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4699</v>
+        <v>1.4209</v>
       </c>
       <c r="N19" t="n">
         <v>182</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6237</v>
+        <v>0.5733</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0231</v>
+        <v>-0.0542</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3621</v>
+        <v>1.2521</v>
       </c>
       <c r="N20" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5946</v>
+        <v>0.5523</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0518</v>
+        <v>-0.0751</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2986</v>
+        <v>1.2063</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5251</v>
+        <v>0.5341</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1202</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1469</v>
+        <v>1.1664</v>
       </c>
       <c r="N22" t="n">
         <v>182</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="C23" t="n">
-        <v>0.421</v>
+        <v>0.3714</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.223</v>
+        <v>-0.2549</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9194</v>
+        <v>0.8112</v>
       </c>
       <c r="N23" t="n">
         <v>172</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="C24" t="n">
-        <v>0.386</v>
+        <v>0.3679</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2574</v>
+        <v>-0.2585</v>
       </c>
       <c r="E24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="F24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="I24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.843</v>
+        <v>0.8034</v>
       </c>
       <c r="N24" t="n">
         <v>139</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1995</v>
+        <v>0.1699</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4413</v>
+        <v>-0.4553</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4357</v>
+        <v>0.371</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1055</v>
+        <v>0.0964</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.534</v>
+        <v>-0.5283</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2305</v>
+        <v>0.2106</v>
       </c>
       <c r="N26" t="n">
         <v>241</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0591</v>
+        <v>0.0641</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5797</v>
+        <v>-0.5605</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1291</v>
+        <v>0.1399</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.004</v>
+        <v>0.0232</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.642</v>
+        <v>-0.6011</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="N28" t="n">
         <v>241</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1481</v>
+        <v>-0.1457</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7841</v>
+        <v>-0.769</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3235</v>
+        <v>-0.3181</v>
       </c>
       <c r="N29" t="n">
         <v>172</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3619</v>
+        <v>-0.418</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1657</v>
+        <v>-0.1914</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8014</v>
+        <v>-0.8145</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3619</v>
+        <v>-0.418</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4664</v>
+        <v>-0.418</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1045</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4664</v>
+        <v>-0.418</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2425</v>
+        <v>-0.418</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1045</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L30" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.138</v>
+        <v>-0.418</v>
       </c>
       <c r="N30" t="n">
-        <v>430</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1704</v>
+        <v>-0.2006</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.806</v>
+        <v>-0.8237</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3722</v>
+        <v>-0.4382</v>
       </c>
       <c r="N31" t="n">
-        <v>139</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3795</v>
+        <v>-0.4483</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1738</v>
+        <v>-0.2053</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8093</v>
+        <v>-0.8283</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3795</v>
+        <v>-0.4483</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3795</v>
+        <v>-0.6535</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.2052</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3795</v>
+        <v>-0.6535</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3795</v>
+        <v>-0.3529</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.2052</v>
       </c>
       <c r="K32" t="n">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3795</v>
+        <v>-0.1477</v>
       </c>
       <c r="N32" t="n">
-        <v>241</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1908</v>
+        <v>-0.2384</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8612</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4167</v>
+        <v>-0.5206</v>
       </c>
       <c r="N33" t="n">
         <v>172</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2279</v>
+        <v>-0.239</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8627</v>
+        <v>-0.8618</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4978</v>
+        <v>-0.5219</v>
       </c>
       <c r="N34" t="n">
         <v>182</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3119</v>
+        <v>-0.3211</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9455</v>
+        <v>-0.9434</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6812</v>
+        <v>-0.7012</v>
       </c>
       <c r="N35" t="n">
         <v>182</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3969</v>
+        <v>-0.4131</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0294</v>
+        <v>-1.0349</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8669</v>
+        <v>-0.9023</v>
       </c>
       <c r="N36" t="n">
         <v>139</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9722</v>
+        <v>-0.9866</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4452</v>
+        <v>-0.4517</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0769</v>
+        <v>-1.0733</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9722</v>
+        <v>-0.9866</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6482</v>
+        <v>-0.6433</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.324</v>
+        <v>-0.3433</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6482</v>
+        <v>-0.6433</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.337</v>
+        <v>-0.3474</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.324</v>
+        <v>-0.3433</v>
       </c>
       <c r="K37" t="n">
         <v>242</v>
@@ -2139,7 +2139,7 @@
         <v>63</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.661</v>
+        <v>-0.6907</v>
       </c>
       <c r="N37" t="n">
         <v>305</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1327</v>
+        <v>-1.1902</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.545</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1494</v>
+        <v>-1.166</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1327</v>
+        <v>-1.1902</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1327</v>
+        <v>-0.008</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1.1822</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1327</v>
+        <v>-0.008</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1327</v>
+        <v>-0.0043</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1.1822</v>
       </c>
       <c r="K38" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1327</v>
+        <v>-1.1865</v>
       </c>
       <c r="N38" t="n">
-        <v>172</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5204</v>
+        <v>-1.2069</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6962</v>
+        <v>-0.5526</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3244</v>
+        <v>-1.1736</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5204</v>
+        <v>-1.2069</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2081</v>
+        <v>-1.2069</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3123</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2081</v>
+        <v>-1.2069</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1082</v>
+        <v>-1.2069</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.3123</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L39" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4205</v>
+        <v>-1.2069</v>
       </c>
       <c r="N39" t="n">
-        <v>323</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1742</v>
+        <v>-1.9593</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.8971</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6196</v>
+        <v>-1.5161</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1742</v>
+        <v>-1.9593</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.3386</v>
+        <v>-3.156</v>
       </c>
       <c r="G40" t="n">
-        <v>1.1644</v>
+        <v>1.1967</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.3386</v>
+        <v>-3.156</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7359</v>
+        <v>-1.7042</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1644</v>
+        <v>1.1967</v>
       </c>
       <c r="K40" t="n">
         <v>198</v>
@@ -2277,7 +2277,7 @@
         <v>232</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.5714999999999999</v>
+        <v>-0.5074999999999998</v>
       </c>
       <c r="N40" t="n">
         <v>430</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5426</v>
+        <v>-3.2489</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6221</v>
+        <v>-1.4876</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.2373</v>
+        <v>-2.1032</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5426</v>
+        <v>-3.2489</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.574</v>
+        <v>-3.2676</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0314</v>
+        <v>0.0187</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.574</v>
+        <v>-3.2676</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8583</v>
+        <v>-1.7644</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0314</v>
+        <v>0.0187</v>
       </c>
       <c r="K41" t="n">
         <v>242</v>
@@ -2323,7 +2323,7 @@
         <v>63</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8269</v>
+        <v>-1.7457</v>
       </c>
       <c r="N41" t="n">
         <v>305</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3873</v>
+        <v>0.3813</v>
       </c>
       <c r="J2" t="n">
-        <v>10.0698</v>
+        <v>9.9138</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1683</v>
+        <v>0.1708</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3758</v>
+        <v>4.4408</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.74</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2829</v>
+        <v>-0.2986</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.3554</v>
+        <v>-7.7636</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3213</v>
+        <v>-0.336</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.3538</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3498</v>
+        <v>-0.3635</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.094799999999999</v>
+        <v>-9.451000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9212</v>
+        <v>0.9014</v>
       </c>
       <c r="J7" t="n">
-        <v>23.9512</v>
+        <v>23.4364</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5947</v>
+        <v>0.5994</v>
       </c>
       <c r="J8" t="n">
-        <v>15.4622</v>
+        <v>15.5844</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.24</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3258</v>
+        <v>0.3431</v>
       </c>
       <c r="J9" t="n">
-        <v>8.470800000000001</v>
+        <v>8.9206</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1122</v>
+        <v>-0.1177</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9172</v>
+        <v>-3.0602</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3306</v>
+        <v>-0.338</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.595599999999999</v>
+        <v>-8.788</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1358</v>
+        <v>1.1396</v>
       </c>
       <c r="J12" t="n">
-        <v>24.9876</v>
+        <v>25.0712</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>1.006</v>
+        <v>0.9586</v>
       </c>
       <c r="J13" t="n">
-        <v>22.132</v>
+        <v>21.0892</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8096</v>
+        <v>0.7729</v>
       </c>
       <c r="J14" t="n">
-        <v>17.8112</v>
+        <v>17.0038</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.651</v>
+        <v>0.6324</v>
       </c>
       <c r="J15" t="n">
-        <v>14.322</v>
+        <v>13.9128</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6274</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>13.8028</v>
+        <v>13.4508</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.99</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0353</v>
+        <v>0.0098</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7766</v>
+        <v>0.2156</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.83</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1805</v>
+        <v>-0.2006</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.971</v>
+        <v>-4.4132</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2011</v>
+        <v>-0.221</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.4242</v>
+        <v>-4.862</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.65</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3519</v>
+        <v>-0.3685</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.7418</v>
+        <v>-8.106999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4734</v>
+        <v>-0.4838</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.4148</v>
+        <v>-10.6436</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9958</v>
+        <v>0.9342</v>
       </c>
       <c r="J22" t="n">
-        <v>34.853</v>
+        <v>32.697</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6031</v>
+        <v>0.5798</v>
       </c>
       <c r="J23" t="n">
-        <v>21.1085</v>
+        <v>20.293</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5533</v>
+        <v>0.5352</v>
       </c>
       <c r="J24" t="n">
-        <v>19.3655</v>
+        <v>18.732</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3225</v>
+        <v>-0.3102</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.2875</v>
+        <v>-10.857</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4387</v>
+        <v>-0.417</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.3545</v>
+        <v>-14.595</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>0.233</v>
+        <v>0.2379</v>
       </c>
       <c r="J27" t="n">
-        <v>8.154999999999999</v>
+        <v>8.326499999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.07</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1903</v>
+        <v>0.1964</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6605</v>
+        <v>6.874</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1219</v>
+        <v>0.1288</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2665</v>
+        <v>4.508</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0608</v>
+        <v>-0.0707</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.128</v>
+        <v>-2.4745</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.333</v>
+        <v>-0.3452</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.655</v>
+        <v>-12.082</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5003</v>
+        <v>0.496</v>
       </c>
       <c r="J32" t="n">
-        <v>14.0084</v>
+        <v>13.888</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2845</v>
+        <v>0.2927</v>
       </c>
       <c r="J33" t="n">
-        <v>7.966</v>
+        <v>8.195600000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1182</v>
+        <v>0.1292</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3096</v>
+        <v>3.6176</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.116</v>
+        <v>-0.127</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.248</v>
+        <v>-3.556</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3216</v>
+        <v>-0.3326</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.004799999999999</v>
+        <v>-9.312799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7113</v>
+        <v>0.7048</v>
       </c>
       <c r="J37" t="n">
-        <v>19.9164</v>
+        <v>19.7344</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.34</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4532</v>
+        <v>0.4632</v>
       </c>
       <c r="J38" t="n">
-        <v>12.6896</v>
+        <v>12.9696</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="J39" t="n">
-        <v>2.3128</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1161</v>
+        <v>-0.124</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.2508</v>
+        <v>-3.472</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1833</v>
+        <v>-0.193</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.1324</v>
+        <v>-5.404</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I42" t="n">
-        <v>1.117</v>
+        <v>1.1003</v>
       </c>
       <c r="J42" t="n">
-        <v>44.68</v>
+        <v>44.012</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6922</v>
+        <v>0.6606</v>
       </c>
       <c r="J43" t="n">
-        <v>27.688</v>
+        <v>26.424</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4965</v>
+        <v>0.4855</v>
       </c>
       <c r="J44" t="n">
-        <v>19.86</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.11</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3428</v>
+        <v>0.3445</v>
       </c>
       <c r="J45" t="n">
-        <v>13.712</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8628</v>
+        <v>-0.7932</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.512</v>
+        <v>-31.728</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6388</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>25.552</v>
+        <v>24.416</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.018</v>
+        <v>0.0129</v>
       </c>
       <c r="J48" t="n">
-        <v>0.72</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1775</v>
+        <v>-0.1933</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.1</v>
+        <v>-7.732</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3159</v>
+        <v>-0.33</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.636</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3255</v>
+        <v>-0.3392</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.02</v>
+        <v>-13.568</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.471</v>
+        <v>0.479</v>
       </c>
       <c r="J52" t="n">
-        <v>14.13</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3519</v>
+        <v>0.3653</v>
       </c>
       <c r="J53" t="n">
-        <v>10.557</v>
+        <v>10.959</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3397</v>
+        <v>0.3535</v>
       </c>
       <c r="J54" t="n">
-        <v>10.191</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1325</v>
+        <v>0.1478</v>
       </c>
       <c r="J55" t="n">
-        <v>3.975</v>
+        <v>4.434</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3673</v>
+        <v>-0.3756</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.019</v>
+        <v>-11.268</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.36</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5662</v>
+        <v>0.5523</v>
       </c>
       <c r="J57" t="n">
-        <v>16.986</v>
+        <v>16.569</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4176</v>
+        <v>0.4146</v>
       </c>
       <c r="J58" t="n">
-        <v>12.528</v>
+        <v>12.438</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2034</v>
+        <v>-0.2182</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.102</v>
+        <v>-6.546</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3406</v>
+        <v>-0.3529</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.218</v>
+        <v>-10.587</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3782</v>
+        <v>-0.3891</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.346</v>
+        <v>-11.673</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8832</v>
+        <v>0.8395</v>
       </c>
       <c r="J62" t="n">
-        <v>26.496</v>
+        <v>25.185</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1748</v>
+        <v>0.1853</v>
       </c>
       <c r="J63" t="n">
-        <v>5.244</v>
+        <v>5.559</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0245</v>
+        <v>-0.0283</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.735</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1504</v>
+        <v>-0.1622</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.512</v>
+        <v>-4.866</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2342</v>
+        <v>-0.2465</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.026</v>
+        <v>-7.395</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0713</v>
+        <v>1.0184</v>
       </c>
       <c r="J67" t="n">
-        <v>32.139</v>
+        <v>30.552</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6925</v>
+        <v>0.6562</v>
       </c>
       <c r="J68" t="n">
-        <v>20.775</v>
+        <v>19.686</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2432</v>
+        <v>0.2481</v>
       </c>
       <c r="J69" t="n">
-        <v>7.296</v>
+        <v>7.443</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4821</v>
+        <v>-0.4589</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.463</v>
+        <v>-13.767</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7192</v>
+        <v>-0.6703</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.576</v>
+        <v>-20.109</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8266</v>
+        <v>0.7825</v>
       </c>
       <c r="J72" t="n">
-        <v>22.3182</v>
+        <v>21.1275</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.06</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1729</v>
+        <v>0.1782</v>
       </c>
       <c r="J73" t="n">
-        <v>4.6683</v>
+        <v>4.8114</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0751</v>
+        <v>0.0799</v>
       </c>
       <c r="J74" t="n">
-        <v>2.0277</v>
+        <v>2.1573</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3686</v>
+        <v>-0.3799</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.952199999999999</v>
+        <v>-10.2573</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4059</v>
+        <v>-0.4157</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.9593</v>
+        <v>-11.2239</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>1.164</v>
+        <v>1.129</v>
       </c>
       <c r="J77" t="n">
-        <v>31.428</v>
+        <v>30.483</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>1.113</v>
+        <v>1.074</v>
       </c>
       <c r="J78" t="n">
-        <v>30.051</v>
+        <v>28.998</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.14</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4085</v>
+        <v>0.4081</v>
       </c>
       <c r="J79" t="n">
-        <v>11.0295</v>
+        <v>11.0187</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2997</v>
+        <v>0.3083</v>
       </c>
       <c r="J80" t="n">
-        <v>8.091900000000001</v>
+        <v>8.3241</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6259</v>
+        <v>-0.581</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.8993</v>
+        <v>-15.687</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2065</v>
+        <v>0.197</v>
       </c>
       <c r="J82" t="n">
-        <v>5.1625</v>
+        <v>4.925</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1174</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.49</v>
+        <v>-2.935</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1965</v>
+        <v>-0.2152</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.9125</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.72</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2915</v>
+        <v>-0.3091</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.2875</v>
+        <v>-7.7275</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4974</v>
+        <v>-0.5056</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.435</v>
+        <v>-12.64</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0225</v>
+        <v>1.1237</v>
       </c>
       <c r="J87" t="n">
-        <v>25.5625</v>
+        <v>28.0925</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9906</v>
       </c>
       <c r="J88" t="n">
-        <v>22.4425</v>
+        <v>24.765</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.37</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6922</v>
+        <v>0.7685</v>
       </c>
       <c r="J89" t="n">
-        <v>17.305</v>
+        <v>19.2125</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1532</v>
+        <v>-0.1408</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.83</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.0275</v>
+        <v>-0.9333</v>
       </c>
       <c r="J91" t="n">
-        <v>-25.6875</v>
+        <v>-23.3325</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4353</v>
+        <v>0.4927</v>
       </c>
       <c r="J92" t="n">
-        <v>13.059</v>
+        <v>14.781</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2267</v>
+        <v>0.243</v>
       </c>
       <c r="J93" t="n">
-        <v>6.801</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1878</v>
+        <v>0.204</v>
       </c>
       <c r="J94" t="n">
-        <v>5.634</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1469</v>
+        <v>0.1625</v>
       </c>
       <c r="J95" t="n">
-        <v>4.407</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1906</v>
+        <v>-0.2012</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.718</v>
+        <v>-6.036</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1925</v>
+        <v>0.2007</v>
       </c>
       <c r="J97" t="n">
-        <v>5.775</v>
+        <v>6.021</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1605</v>
+        <v>0.1691</v>
       </c>
       <c r="J98" t="n">
-        <v>4.815</v>
+        <v>5.073</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0614</v>
+        <v>-0.0711</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.842</v>
+        <v>-2.133</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1539</v>
+        <v>-0.1675</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.617</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.88</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1539</v>
+        <v>-0.1675</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.617</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4254</v>
+        <v>0.4594</v>
       </c>
       <c r="J102" t="n">
-        <v>11.0604</v>
+        <v>11.9444</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1172</v>
+        <v>-0.1339</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.0472</v>
+        <v>-3.4814</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.258</v>
+        <v>-0.2753</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.708</v>
+        <v>-7.1578</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3156</v>
+        <v>-0.3315</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.2056</v>
+        <v>-8.619</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3817</v>
+        <v>-0.3951</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.924200000000001</v>
+        <v>-10.2726</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.47</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8237</v>
+        <v>0.9107</v>
       </c>
       <c r="J107" t="n">
-        <v>21.4162</v>
+        <v>23.6782</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5606</v>
+        <v>0.623</v>
       </c>
       <c r="J108" t="n">
-        <v>14.5756</v>
+        <v>16.198</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.493</v>
+        <v>0.5471</v>
       </c>
       <c r="J109" t="n">
-        <v>12.818</v>
+        <v>14.2246</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3607</v>
+        <v>0.3821</v>
       </c>
       <c r="J110" t="n">
-        <v>9.3782</v>
+        <v>9.9346</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0785</v>
+        <v>0.1</v>
       </c>
       <c r="J111" t="n">
-        <v>2.041</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6193</v>
+        <v>0.6869</v>
       </c>
       <c r="J112" t="n">
-        <v>16.7211</v>
+        <v>18.5463</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.551</v>
+        <v>0.6113</v>
       </c>
       <c r="J113" t="n">
-        <v>14.877</v>
+        <v>16.5051</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4105</v>
+        <v>0.4517</v>
       </c>
       <c r="J114" t="n">
-        <v>11.0835</v>
+        <v>12.1959</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3647</v>
+        <v>0.3867</v>
       </c>
       <c r="J115" t="n">
-        <v>9.8469</v>
+        <v>10.4409</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.11</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3289</v>
+        <v>0.3369</v>
       </c>
       <c r="J116" t="n">
-        <v>8.8803</v>
+        <v>9.096299999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.06</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1964</v>
+        <v>0.1953</v>
       </c>
       <c r="J117" t="n">
-        <v>5.3028</v>
+        <v>5.2731</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0268</v>
+        <v>0.0193</v>
       </c>
       <c r="J118" t="n">
-        <v>0.7236</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0268</v>
+        <v>0.0193</v>
       </c>
       <c r="J119" t="n">
-        <v>0.7236</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2044</v>
+        <v>-0.2212</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.5188</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.489</v>
+        <v>-0.4961</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.203</v>
+        <v>-13.3947</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0866</v>
+        <v>1.1871</v>
       </c>
       <c r="J122" t="n">
-        <v>39.1176</v>
+        <v>42.7356</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5588</v>
+        <v>0.6181</v>
       </c>
       <c r="J123" t="n">
-        <v>20.1168</v>
+        <v>22.2516</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2279</v>
+        <v>0.2377</v>
       </c>
       <c r="J124" t="n">
-        <v>8.2044</v>
+        <v>8.5572</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.061</v>
+        <v>0.0771</v>
       </c>
       <c r="J125" t="n">
-        <v>2.196</v>
+        <v>2.7756</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8633</v>
+        <v>-0.7935</v>
       </c>
       <c r="J126" t="n">
-        <v>-31.0788</v>
+        <v>-28.566</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7008</v>
+        <v>0.7789</v>
       </c>
       <c r="J127" t="n">
-        <v>25.2288</v>
+        <v>28.0404</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2358</v>
+        <v>0.2399</v>
       </c>
       <c r="J128" t="n">
-        <v>8.488799999999999</v>
+        <v>8.6364</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2345</v>
+        <v>-0.2489</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.442</v>
+        <v>-8.9604</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2838</v>
+        <v>-0.2974</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.2168</v>
+        <v>-10.7064</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3508</v>
+        <v>-0.3626</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.6288</v>
+        <v>-13.0536</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.88</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6529</v>
+        <v>1.6379</v>
       </c>
       <c r="J132" t="n">
-        <v>44.6283</v>
+        <v>44.2233</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6075</v>
+        <v>0.5828</v>
       </c>
       <c r="J133" t="n">
-        <v>16.4025</v>
+        <v>15.7356</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5715</v>
+        <v>-0.5376</v>
       </c>
       <c r="J134" t="n">
-        <v>-15.4305</v>
+        <v>-14.5152</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.598</v>
+        <v>-0.5613</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.146</v>
+        <v>-15.1551</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.676</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.6371</v>
+        <v>-18.252</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5589</v>
+        <v>0.5454</v>
       </c>
       <c r="J137" t="n">
-        <v>15.0903</v>
+        <v>14.7258</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3214</v>
+        <v>0.3249</v>
       </c>
       <c r="J138" t="n">
-        <v>8.6778</v>
+        <v>8.7723</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2627</v>
+        <v>0.269</v>
       </c>
       <c r="J139" t="n">
-        <v>7.0929</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1687</v>
+        <v>-0.1816</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.5549</v>
+        <v>-4.9032</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3475</v>
+        <v>-0.3582</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.3825</v>
+        <v>-9.6714</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0725</v>
+        <v>1.0255</v>
       </c>
       <c r="J142" t="n">
-        <v>25.74</v>
+        <v>24.612</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8275</v>
+        <v>0.7808</v>
       </c>
       <c r="J143" t="n">
-        <v>19.86</v>
+        <v>18.7392</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3923</v>
+        <v>0.391</v>
       </c>
       <c r="J144" t="n">
-        <v>9.4152</v>
+        <v>9.384</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0944</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.2656</v>
+        <v>-2.088</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.95</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2412</v>
+        <v>-0.2308</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.7888</v>
+        <v>-5.5392</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.3</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6489</v>
+        <v>0.6208</v>
       </c>
       <c r="J147" t="n">
-        <v>15.5736</v>
+        <v>14.8992</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1372</v>
+        <v>-0.152</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.2928</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.82</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.21</v>
+        <v>-0.2255</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.04</v>
+        <v>-5.412</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.21</v>
+        <v>-0.2255</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.04</v>
+        <v>-5.412</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2301</v>
+        <v>-0.2455</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.5224</v>
+        <v>-5.892</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2175</v>
+        <v>-0.2421</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.915</v>
+        <v>-4.3578</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3173</v>
+        <v>-0.3383</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.7114</v>
+        <v>-6.0894</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3439</v>
+        <v>-0.3641</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.1902</v>
+        <v>-6.5538</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3796</v>
+        <v>-0.3984</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.8328</v>
+        <v>-7.1712</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.53</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4446</v>
+        <v>-0.4598</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.002800000000001</v>
+        <v>-8.276400000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8258</v>
+        <v>0.8216</v>
       </c>
       <c r="J157" t="n">
-        <v>14.8644</v>
+        <v>14.7888</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7383</v>
+        <v>0.7405</v>
       </c>
       <c r="J158" t="n">
-        <v>13.2894</v>
+        <v>13.329</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.52</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6015</v>
+        <v>0.6121</v>
       </c>
       <c r="J159" t="n">
-        <v>10.827</v>
+        <v>11.0178</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5311</v>
+        <v>0.5454</v>
       </c>
       <c r="J160" t="n">
-        <v>9.559799999999999</v>
+        <v>9.8172</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.24</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2975</v>
+        <v>0.3217</v>
       </c>
       <c r="J161" t="n">
-        <v>5.355</v>
+        <v>5.7906</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7409</v>
+        <v>0.699</v>
       </c>
       <c r="J162" t="n">
-        <v>20.0043</v>
+        <v>18.873</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3275</v>
+        <v>0.3273</v>
       </c>
       <c r="J163" t="n">
-        <v>8.842499999999999</v>
+        <v>8.8371</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.09</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2996</v>
+        <v>0.3013</v>
       </c>
       <c r="J164" t="n">
-        <v>8.0892</v>
+        <v>8.1351</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0162</v>
+        <v>-0.0111</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.4374</v>
+        <v>-0.2997</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3109</v>
+        <v>-0.3021</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.394299999999999</v>
+        <v>-8.156700000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9759</v>
+        <v>0.9246</v>
       </c>
       <c r="J167" t="n">
-        <v>26.3493</v>
+        <v>24.9642</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4551</v>
+        <v>0.4493</v>
       </c>
       <c r="J168" t="n">
-        <v>12.2877</v>
+        <v>12.1311</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1886</v>
+        <v>-0.202</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.0922</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2195</v>
+        <v>-0.2329</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9265</v>
+        <v>-6.2883</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4023</v>
+        <v>-0.4113</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.8621</v>
+        <v>-11.1051</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.758</v>
+        <v>0.7109</v>
       </c>
       <c r="J172" t="n">
-        <v>21.982</v>
+        <v>20.6161</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.19</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5808</v>
+        <v>0.5543</v>
       </c>
       <c r="J173" t="n">
-        <v>16.8432</v>
+        <v>16.0747</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1568</v>
+        <v>0.1637</v>
       </c>
       <c r="J174" t="n">
-        <v>4.5472</v>
+        <v>4.7473</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2062</v>
+        <v>-0.2065</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.9798</v>
+        <v>-5.9885</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8093</v>
+        <v>-0.7512</v>
       </c>
       <c r="J176" t="n">
-        <v>-23.4697</v>
+        <v>-21.7848</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.28</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5542</v>
+        <v>0.5451</v>
       </c>
       <c r="J177" t="n">
-        <v>16.0718</v>
+        <v>15.8079</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.415</v>
+        <v>0.4164</v>
       </c>
       <c r="J178" t="n">
-        <v>12.035</v>
+        <v>12.0756</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2296</v>
+        <v>0.2404</v>
       </c>
       <c r="J179" t="n">
-        <v>6.6584</v>
+        <v>6.9716</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0848</v>
+        <v>-0.093</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.4592</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1437</v>
+        <v>-0.1543</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.1673</v>
+        <v>-4.4747</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.94</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5763</v>
+        <v>1.5807</v>
       </c>
       <c r="J182" t="n">
-        <v>26.7971</v>
+        <v>26.8719</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.85</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4775</v>
+        <v>1.4766</v>
       </c>
       <c r="J183" t="n">
-        <v>25.1175</v>
+        <v>25.1022</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.61</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2111</v>
+        <v>1.1919</v>
       </c>
       <c r="J184" t="n">
-        <v>20.5887</v>
+        <v>20.2623</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.33</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7832</v>
+        <v>0.7587</v>
       </c>
       <c r="J185" t="n">
-        <v>13.3144</v>
+        <v>12.8979</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.3</v>
       </c>
       <c r="I186" t="n">
-        <v>0.7156</v>
+        <v>0.6992</v>
       </c>
       <c r="J186" t="n">
-        <v>12.1652</v>
+        <v>11.8864</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0619</v>
+        <v>-0.0032</v>
       </c>
       <c r="J187" t="n">
-        <v>1.0523</v>
+        <v>-0.0544</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.401</v>
+        <v>-0.4215</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.817</v>
+        <v>-7.1655</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.5</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4539</v>
+        <v>-0.4715</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.7163</v>
+        <v>-8.015499999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5393</v>
+        <v>-0.5507</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.168100000000001</v>
+        <v>-9.3619</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.31</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.637</v>
+        <v>-0.6402</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.829</v>
+        <v>-10.8834</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.91</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5592</v>
+        <v>1.56</v>
       </c>
       <c r="J192" t="n">
-        <v>31.184</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.71</v>
       </c>
       <c r="I193" t="n">
-        <v>1.3337</v>
+        <v>1.3214</v>
       </c>
       <c r="J193" t="n">
-        <v>26.674</v>
+        <v>26.428</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1845</v>
+        <v>1.1615</v>
       </c>
       <c r="J194" t="n">
-        <v>23.69</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.37</v>
       </c>
       <c r="I195" t="n">
-        <v>0.888</v>
+        <v>0.8476</v>
       </c>
       <c r="J195" t="n">
-        <v>17.76</v>
+        <v>16.952</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0227</v>
+        <v>0.0185</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.454</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.96</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0922</v>
+        <v>0.0286</v>
       </c>
       <c r="J197" t="n">
-        <v>1.844</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.63</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3398</v>
+        <v>-0.3627</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.796</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4305</v>
+        <v>-0.4488</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.37</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5825</v>
+        <v>-0.5899</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.65</v>
+        <v>-11.798</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6116</v>
+        <v>-0.6166</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.232</v>
+        <v>-12.332</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0461</v>
+        <v>-0.063</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.0603</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.86</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1525</v>
+        <v>-0.1718</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.5075</v>
+        <v>-3.9514</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1942</v>
+        <v>-0.2134</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.4666</v>
+        <v>-4.9082</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3174</v>
+        <v>-0.3347</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.3002</v>
+        <v>-7.6981</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4114</v>
+        <v>-0.4247</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.462199999999999</v>
+        <v>-9.7681</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.69</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7869</v>
       </c>
       <c r="J207" t="n">
-        <v>18.2344</v>
+        <v>18.0987</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6076</v>
+        <v>0.6148</v>
       </c>
       <c r="J208" t="n">
-        <v>13.9748</v>
+        <v>14.1404</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.39</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4811</v>
+        <v>0.4952</v>
       </c>
       <c r="J209" t="n">
-        <v>11.0653</v>
+        <v>11.3896</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.21</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2786</v>
+        <v>0.2996</v>
       </c>
       <c r="J210" t="n">
-        <v>6.4078</v>
+        <v>6.8908</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.0698</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.6054</v>
+        <v>-1.587</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.29</v>
       </c>
       <c r="I212" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J212" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>2.14</v>
       </c>
       <c r="I213" t="n">
-        <v>1.7827</v>
+        <v>1.7983</v>
       </c>
       <c r="J213" t="n">
-        <v>32.0886</v>
+        <v>32.3694</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.52</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1038</v>
+        <v>1.0765</v>
       </c>
       <c r="J214" t="n">
-        <v>19.8684</v>
+        <v>19.377</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6372</v>
+        <v>0.6317</v>
       </c>
       <c r="J215" t="n">
-        <v>11.4696</v>
+        <v>11.3706</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1329</v>
       </c>
       <c r="J216" t="n">
-        <v>1.6002</v>
+        <v>2.3922</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2012</v>
+        <v>-0.2367</v>
       </c>
       <c r="J217" t="n">
-        <v>-3.6216</v>
+        <v>-4.2606</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.59</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3564</v>
+        <v>-0.3821</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.4152</v>
+        <v>-6.8778</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3871</v>
+        <v>-0.4107</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.9678</v>
+        <v>-7.3926</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.31</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6257</v>
+        <v>-0.6314</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.2626</v>
+        <v>-11.3652</v>
       </c>
     </row>
     <row r="221">
@@ -11229,10 +11229,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8396</v>
       </c>
       <c r="J222" t="n">
-        <v>21.3264</v>
+        <v>20.1504</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8008</v>
       </c>
       <c r="J223" t="n">
-        <v>20.2632</v>
+        <v>19.2192</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.31</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7617</v>
       </c>
       <c r="J224" t="n">
-        <v>19.1976</v>
+        <v>18.2808</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7331</v>
+        <v>0.7026</v>
       </c>
       <c r="J225" t="n">
-        <v>17.5944</v>
+        <v>16.8624</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1986</v>
+        <v>0.2173</v>
       </c>
       <c r="J226" t="n">
-        <v>4.7664</v>
+        <v>5.2152</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.21</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5065</v>
       </c>
       <c r="J227" t="n">
-        <v>12.7872</v>
+        <v>12.156</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2636</v>
+        <v>0.2553</v>
       </c>
       <c r="J228" t="n">
-        <v>6.3264</v>
+        <v>6.1272</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1988</v>
+        <v>-0.2169</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.7712</v>
+        <v>-5.2056</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3618</v>
+        <v>-0.3763</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.683199999999999</v>
+        <v>-9.0312</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.61</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.64</v>
+        <v>-14.6496</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2481</v>
+        <v>1.2196</v>
       </c>
       <c r="J232" t="n">
-        <v>33.6987</v>
+        <v>32.9292</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.33</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8542</v>
+        <v>0.8076</v>
       </c>
       <c r="J233" t="n">
-        <v>23.0634</v>
+        <v>21.8052</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.32</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8316</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>22.4532</v>
+        <v>21.2706</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0556</v>
+        <v>-0.0384</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.5012</v>
+        <v>-1.0368</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4104</v>
+        <v>-0.385</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.0808</v>
+        <v>-10.395</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4045</v>
+        <v>0.3976</v>
       </c>
       <c r="J237" t="n">
-        <v>10.9215</v>
+        <v>10.7352</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1164</v>
+        <v>-0.1303</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.1428</v>
+        <v>-3.5181</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1274</v>
+        <v>-0.1416</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.4398</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1274</v>
+        <v>-0.1416</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.4398</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2313</v>
+        <v>-0.2464</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.2451</v>
+        <v>-6.6528</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.63</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3321</v>
+        <v>1.3028</v>
       </c>
       <c r="J242" t="n">
-        <v>37.2988</v>
+        <v>36.4784</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7487</v>
+        <v>0.7088</v>
       </c>
       <c r="J243" t="n">
-        <v>20.9636</v>
+        <v>19.8464</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0276</v>
+        <v>-0.0189</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.7728</v>
+        <v>-0.5292</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.85</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5221</v>
+        <v>-0.4924</v>
       </c>
       <c r="J245" t="n">
-        <v>-14.6188</v>
+        <v>-13.7872</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5491</v>
+        <v>-0.5167</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.3748</v>
+        <v>-14.4676</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7625</v>
+        <v>0.7299</v>
       </c>
       <c r="J247" t="n">
-        <v>21.35</v>
+        <v>20.4372</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3771</v>
+        <v>0.3776</v>
       </c>
       <c r="J248" t="n">
-        <v>10.5588</v>
+        <v>10.5728</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.95</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0779</v>
+        <v>-0.0876</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.1812</v>
+        <v>-2.4528</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2413</v>
+        <v>-0.2542</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.7564</v>
+        <v>-7.1176</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2513</v>
+        <v>-0.2641</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.0364</v>
+        <v>-7.3948</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0188</v>
+        <v>0.9678</v>
       </c>
       <c r="J252" t="n">
-        <v>22.4136</v>
+        <v>21.2916</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0188</v>
+        <v>0.9678</v>
       </c>
       <c r="J253" t="n">
-        <v>22.4136</v>
+        <v>21.2916</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8858</v>
+        <v>0.8377</v>
       </c>
       <c r="J254" t="n">
-        <v>19.4876</v>
+        <v>18.4294</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.19</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5212</v>
+        <v>0.5133</v>
       </c>
       <c r="J255" t="n">
-        <v>11.4664</v>
+        <v>11.2926</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.02</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0279</v>
+        <v>0.054</v>
       </c>
       <c r="J256" t="n">
-        <v>0.6138</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2564</v>
+        <v>0.25</v>
       </c>
       <c r="J257" t="n">
-        <v>5.6408</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.96</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0453</v>
+        <v>-0.0588</v>
       </c>
       <c r="J258" t="n">
-        <v>-0.9966</v>
+        <v>-1.2936</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1402</v>
+        <v>-0.1572</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.0844</v>
+        <v>-3.4584</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2784</v>
+        <v>-0.2951</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.1248</v>
+        <v>-6.4922</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4479</v>
+        <v>-0.4579</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.8538</v>
+        <v>-10.0738</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7948</v>
+        <v>0.7659</v>
       </c>
       <c r="J262" t="n">
-        <v>23.0492</v>
+        <v>22.2111</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.224</v>
+        <v>0.2348</v>
       </c>
       <c r="J263" t="n">
-        <v>6.496</v>
+        <v>6.8092</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0045</v>
+        <v>-0.0034</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.1305</v>
+        <v>-0.09859999999999999</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2047</v>
+        <v>-0.2169</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.9363</v>
+        <v>-6.2901</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3042</v>
+        <v>-0.3153</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.8218</v>
+        <v>-9.143700000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2515</v>
+        <v>0.2647</v>
       </c>
       <c r="J267" t="n">
-        <v>7.2935</v>
+        <v>7.6763</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1401</v>
+        <v>0.1534</v>
       </c>
       <c r="J268" t="n">
-        <v>4.0629</v>
+        <v>4.4486</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0436</v>
+        <v>0.052</v>
       </c>
       <c r="J269" t="n">
-        <v>1.2644</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0396</v>
+        <v>-0.0455</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.1484</v>
+        <v>-1.3195</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0672</v>
+        <v>-0.0756</v>
       </c>
       <c r="J271" t="n">
-        <v>-1.9488</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7038</v>
+        <v>0.6641</v>
       </c>
       <c r="J272" t="n">
-        <v>20.4102</v>
+        <v>19.2589</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.04</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1556</v>
+        <v>0.1629</v>
       </c>
       <c r="J273" t="n">
-        <v>4.5124</v>
+        <v>4.7241</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.02</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0859</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J274" t="n">
-        <v>2.4911</v>
+        <v>2.7347</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0455</v>
+        <v>0.0534</v>
       </c>
       <c r="J275" t="n">
-        <v>1.3195</v>
+        <v>1.5486</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3323</v>
+        <v>-0.3238</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.636699999999999</v>
+        <v>-9.3902</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6029</v>
       </c>
       <c r="J277" t="n">
-        <v>17.9945</v>
+        <v>17.4841</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3159</v>
+        <v>0.3209</v>
       </c>
       <c r="J278" t="n">
-        <v>9.161099999999999</v>
+        <v>9.306100000000001</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2378</v>
+        <v>0.2463</v>
       </c>
       <c r="J279" t="n">
-        <v>6.8962</v>
+        <v>7.1427</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.213</v>
+        <v>-0.2256</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.177</v>
+        <v>-6.5424</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2333</v>
+        <v>-0.2458</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.7657</v>
+        <v>-7.1282</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.1787</v>
+        <v>0.1866</v>
       </c>
       <c r="J282" t="n">
-        <v>5.361</v>
+        <v>5.598</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0032</v>
+        <v>0.0023</v>
       </c>
       <c r="J283" t="n">
-        <v>0.096</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.99</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0186</v>
+        <v>-0.0238</v>
       </c>
       <c r="J284" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.714</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.97</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0478</v>
+        <v>-0.0565</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.434</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2355</v>
+        <v>-0.2497</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.065</v>
+        <v>-7.491</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6625</v>
+        <v>0.6586</v>
       </c>
       <c r="J287" t="n">
-        <v>19.875</v>
+        <v>19.758</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.213</v>
+        <v>0.2295</v>
       </c>
       <c r="J288" t="n">
-        <v>6.39</v>
+        <v>6.885</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2002</v>
+        <v>0.2166</v>
       </c>
       <c r="J289" t="n">
-        <v>6.006</v>
+        <v>6.498</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0116</v>
+        <v>-0.0089</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.348</v>
+        <v>-0.267</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2019</v>
+        <v>-0.2124</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.057</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.133</v>
+        <v>1.0918</v>
       </c>
       <c r="J292" t="n">
-        <v>30.591</v>
+        <v>29.4786</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6839</v>
       </c>
       <c r="J293" t="n">
-        <v>19.4211</v>
+        <v>18.4653</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3975</v>
+        <v>0.3945</v>
       </c>
       <c r="J294" t="n">
-        <v>10.7325</v>
+        <v>10.6515</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2656</v>
+        <v>-0.2558</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.1712</v>
+        <v>-6.9066</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.86</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4991</v>
+        <v>-0.4708</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.4757</v>
+        <v>-12.7116</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.23</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5158</v>
+        <v>0.5007</v>
       </c>
       <c r="J297" t="n">
-        <v>13.9266</v>
+        <v>13.5189</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0154</v>
+        <v>-0.0214</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.4158</v>
+        <v>-0.5778</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0711</v>
+        <v>-0.0824</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.9197</v>
+        <v>-2.2248</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.32</v>
+        <v>-4.7223</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.66</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.367</v>
+        <v>-0.3786</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.909000000000001</v>
+        <v>-10.2222</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.57</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2283</v>
+        <v>1.1975</v>
       </c>
       <c r="J302" t="n">
-        <v>33.1641</v>
+        <v>32.3325</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.35</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9048</v>
+        <v>0.8511</v>
       </c>
       <c r="J303" t="n">
-        <v>24.4296</v>
+        <v>22.9797</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>0.511</v>
+        <v>0.501</v>
       </c>
       <c r="J304" t="n">
-        <v>13.797</v>
+        <v>13.527</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1503</v>
+        <v>0.1681</v>
       </c>
       <c r="J305" t="n">
-        <v>4.0581</v>
+        <v>4.5387</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4342</v>
+        <v>-0.4079</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.7234</v>
+        <v>-11.0133</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6704</v>
+        <v>0.6425</v>
       </c>
       <c r="J307" t="n">
-        <v>18.1008</v>
+        <v>17.3475</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2585</v>
+        <v>0.2613</v>
       </c>
       <c r="J308" t="n">
-        <v>6.9795</v>
+        <v>7.0551</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1294</v>
+        <v>-0.1432</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.4938</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1724</v>
+        <v>-0.187</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.6548</v>
+        <v>-5.049</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4245</v>
+        <v>-0.4335</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.4615</v>
+        <v>-11.7045</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.27</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3668</v>
+        <v>0.3815</v>
       </c>
       <c r="J312" t="n">
-        <v>12.838</v>
+        <v>13.3525</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3431</v>
+        <v>0.3586</v>
       </c>
       <c r="J313" t="n">
-        <v>12.0085</v>
+        <v>12.551</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1956</v>
+        <v>0.2133</v>
       </c>
       <c r="J314" t="n">
-        <v>6.846</v>
+        <v>7.4655</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1956</v>
+        <v>0.2133</v>
       </c>
       <c r="J315" t="n">
-        <v>6.846</v>
+        <v>7.4655</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.12</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1822</v>
+        <v>0.1998</v>
       </c>
       <c r="J316" t="n">
-        <v>6.377</v>
+        <v>6.993</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2477</v>
+        <v>0.2491</v>
       </c>
       <c r="J317" t="n">
-        <v>8.669499999999999</v>
+        <v>8.718500000000001</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0186</v>
+        <v>0.0137</v>
       </c>
       <c r="J318" t="n">
-        <v>0.651</v>
+        <v>0.4795</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0653</v>
+        <v>-0.078</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.2855</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2939</v>
+        <v>-0.3091</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.2865</v>
+        <v>-10.8185</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3793</v>
+        <v>-0.3916</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.2755</v>
+        <v>-13.706</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4759</v>
+        <v>0.4539</v>
       </c>
       <c r="J322" t="n">
-        <v>11.8975</v>
+        <v>11.3475</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.83</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1891</v>
+        <v>-0.2071</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.7275</v>
+        <v>-5.1775</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2081</v>
+        <v>-0.2263</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.2025</v>
+        <v>-5.6575</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2853</v>
+        <v>-0.3024</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.1325</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.57</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.436</v>
+        <v>-0.4471</v>
       </c>
       <c r="J326" t="n">
-        <v>-10.9</v>
+        <v>-11.1775</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.72</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3683</v>
+        <v>1.3539</v>
       </c>
       <c r="J327" t="n">
-        <v>34.2075</v>
+        <v>33.8475</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1421</v>
+        <v>1.1122</v>
       </c>
       <c r="J328" t="n">
-        <v>28.5525</v>
+        <v>27.805</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.52</v>
       </c>
       <c r="I329" t="n">
-        <v>1.13</v>
+        <v>1.0991</v>
       </c>
       <c r="J329" t="n">
-        <v>28.25</v>
+        <v>27.4775</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.35</v>
       </c>
       <c r="I330" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8259</v>
       </c>
       <c r="J330" t="n">
-        <v>21.71</v>
+        <v>20.6475</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6635</v>
+        <v>-0.6075</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.5875</v>
+        <v>-15.1875</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.18</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3987</v>
+        <v>0.3971</v>
       </c>
       <c r="J332" t="n">
-        <v>16.7454</v>
+        <v>16.6782</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.09</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2235</v>
+        <v>0.231</v>
       </c>
       <c r="J333" t="n">
-        <v>9.387</v>
+        <v>9.702</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.06</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1597</v>
+        <v>0.1687</v>
       </c>
       <c r="J334" t="n">
-        <v>6.7074</v>
+        <v>7.0854</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0902</v>
+        <v>0.0988</v>
       </c>
       <c r="J335" t="n">
-        <v>3.7884</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3468</v>
+        <v>-0.3577</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.5656</v>
+        <v>-15.0234</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.57</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2639</v>
+        <v>1.2291</v>
       </c>
       <c r="J337" t="n">
-        <v>53.0838</v>
+        <v>51.6222</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3241</v>
+        <v>0.325</v>
       </c>
       <c r="J338" t="n">
-        <v>13.6122</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2399</v>
+        <v>0.2458</v>
       </c>
       <c r="J339" t="n">
-        <v>10.0758</v>
+        <v>10.3236</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.89</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4038</v>
+        <v>-0.3866</v>
       </c>
       <c r="J340" t="n">
-        <v>-16.9596</v>
+        <v>-16.2372</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5688</v>
+        <v>-0.5357</v>
       </c>
       <c r="J341" t="n">
-        <v>-23.8896</v>
+        <v>-22.4994</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.26</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5462</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J342" t="n">
-        <v>15.8398</v>
+        <v>15.4512</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.03</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0915</v>
+        <v>0.0997</v>
       </c>
       <c r="J343" t="n">
-        <v>2.6535</v>
+        <v>2.8913</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.99</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0207</v>
+        <v>-0.0253</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.7337</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1564</v>
+        <v>-0.1695</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.5356</v>
+        <v>-4.9155</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.1882</v>
+        <v>-0.2017</v>
       </c>
       <c r="J346" t="n">
-        <v>-5.4578</v>
+        <v>-5.8493</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6858</v>
+        <v>0.6515</v>
       </c>
       <c r="J347" t="n">
-        <v>19.8882</v>
+        <v>18.8935</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.5099</v>
+        <v>0.4947</v>
       </c>
       <c r="J348" t="n">
-        <v>14.7871</v>
+        <v>14.3463</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.17</v>
       </c>
       <c r="I349" t="n">
-        <v>0.5099</v>
+        <v>0.4947</v>
       </c>
       <c r="J349" t="n">
-        <v>14.7871</v>
+        <v>14.3463</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1161</v>
+        <v>-0.1149</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.3669</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4032</v>
+        <v>-0.3862</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.6928</v>
+        <v>-11.1998</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.92</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.0593</v>
+        <v>-0.083</v>
       </c>
       <c r="J352" t="n">
-        <v>-1.186</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.91</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.438</v>
+        <v>-1.914</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.7</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.2963</v>
+        <v>-0.3167</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.926</v>
+        <v>-6.334</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.55</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.434</v>
+        <v>-0.4485</v>
       </c>
       <c r="J355" t="n">
-        <v>-8.68</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.36</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.6118</v>
+        <v>-0.6143</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.236</v>
+        <v>-12.286</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3809</v>
+        <v>1.3671</v>
       </c>
       <c r="J357" t="n">
-        <v>27.618</v>
+        <v>27.342</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.66</v>
       </c>
       <c r="I358" t="n">
-        <v>1.2983</v>
+        <v>1.2795</v>
       </c>
       <c r="J358" t="n">
-        <v>25.966</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.3</v>
       </c>
       <c r="I359" t="n">
-        <v>0.7591</v>
+        <v>0.7295</v>
       </c>
       <c r="J359" t="n">
-        <v>15.182</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.26</v>
       </c>
       <c r="I360" t="n">
-        <v>0.6674</v>
+        <v>0.6483</v>
       </c>
       <c r="J360" t="n">
-        <v>13.348</v>
+        <v>12.966</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2247</v>
+        <v>-0.2015</v>
       </c>
       <c r="J361" t="n">
-        <v>-4.494</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.76</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4138</v>
+        <v>1.4024</v>
       </c>
       <c r="J362" t="n">
-        <v>29.6898</v>
+        <v>29.4504</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.73</v>
       </c>
       <c r="I363" t="n">
-        <v>1.3788</v>
+        <v>1.3653</v>
       </c>
       <c r="J363" t="n">
-        <v>28.9548</v>
+        <v>28.6713</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.37</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9097</v>
+        <v>0.8628</v>
       </c>
       <c r="J364" t="n">
-        <v>19.1037</v>
+        <v>18.1188</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.21</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5405</v>
       </c>
       <c r="J365" t="n">
-        <v>11.4639</v>
+        <v>11.3505</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.9</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4471</v>
+        <v>-0.4108</v>
       </c>
       <c r="J366" t="n">
-        <v>-9.389099999999999</v>
+        <v>-8.626799999999999</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>0.93</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.0496</v>
+        <v>-0.0723</v>
       </c>
       <c r="J367" t="n">
-        <v>-1.0416</v>
+        <v>-1.5183</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.91</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.5729</v>
+        <v>-2.0601</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.63</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3609</v>
+        <v>-0.3789</v>
       </c>
       <c r="J369" t="n">
-        <v>-7.5789</v>
+        <v>-7.9569</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.53</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4544</v>
+        <v>-0.4674</v>
       </c>
       <c r="J370" t="n">
-        <v>-9.542400000000001</v>
+        <v>-9.8154</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.49</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4918</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.3278</v>
+        <v>-10.5525</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.78</v>
       </c>
       <c r="I372" t="n">
-        <v>1.4412</v>
+        <v>1.4306</v>
       </c>
       <c r="J372" t="n">
-        <v>33.1476</v>
+        <v>32.9038</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.63</v>
       </c>
       <c r="I373" t="n">
-        <v>1.2642</v>
+        <v>1.2428</v>
       </c>
       <c r="J373" t="n">
-        <v>29.0766</v>
+        <v>28.5844</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.27</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6923</v>
+        <v>0.6701</v>
       </c>
       <c r="J374" t="n">
-        <v>15.9229</v>
+        <v>15.4123</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.3177</v>
+        <v>0.3332</v>
       </c>
       <c r="J375" t="n">
-        <v>7.3071</v>
+        <v>7.6636</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I376" t="n">
-        <v>0.2039</v>
+        <v>0.2281</v>
       </c>
       <c r="J376" t="n">
-        <v>4.6897</v>
+        <v>5.2463</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.01</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1508</v>
+        <v>0.1261</v>
       </c>
       <c r="J377" t="n">
-        <v>3.4684</v>
+        <v>2.9003</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.83</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1686</v>
+        <v>-0.1913</v>
       </c>
       <c r="J378" t="n">
-        <v>-3.8778</v>
+        <v>-4.3999</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.6</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.3895</v>
+        <v>-0.4061</v>
       </c>
       <c r="J379" t="n">
-        <v>-8.958500000000001</v>
+        <v>-9.340299999999999</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.58</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4082</v>
+        <v>-0.4238</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.3886</v>
+        <v>-9.747400000000001</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.49</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.4924</v>
+        <v>-0.503</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.3252</v>
+        <v>-11.569</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3133/event_3133_evp_summary.xlsx
+++ b/database/event/3133/event_3133_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.770300000000001</v>
+        <v>8.546200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0158</v>
+        <v>3.9131</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3682</v>
+        <v>3.2874</v>
       </c>
       <c r="E2" t="n">
-        <v>8.770300000000001</v>
+        <v>8.546200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9516</v>
+        <v>3.8182</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8187</v>
+        <v>4.728</v>
       </c>
       <c r="H2" t="n">
-        <v>8.143599999999999</v>
+        <v>7.8927</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3975</v>
+        <v>4.4315</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8187</v>
+        <v>4.728</v>
       </c>
       <c r="K2" t="n">
         <v>109</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>9.216200000000001</v>
+        <v>9.1595</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4125</v>
+        <v>6.2213</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9362</v>
+        <v>2.8486</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2949</v>
+        <v>2.2283</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4125</v>
+        <v>6.2213</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9436</v>
+        <v>3.819</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4689</v>
+        <v>2.4023</v>
       </c>
       <c r="H3" t="n">
-        <v>8.1173</v>
+        <v>7.8957</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3833</v>
+        <v>4.4332</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4689</v>
+        <v>2.4023</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8522</v>
+        <v>6.8355</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2509</v>
+        <v>5.9939</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8622</v>
+        <v>2.7445</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2213</v>
+        <v>2.1247</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2509</v>
+        <v>5.9939</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8671</v>
+        <v>3.7529</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3838</v>
+        <v>2.241</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8648</v>
+        <v>7.6473</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2469</v>
+        <v>4.2937</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3838</v>
+        <v>2.241</v>
       </c>
       <c r="K4" t="n">
         <v>109</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6307</v>
+        <v>6.534700000000001</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4899</v>
+        <v>5.4363</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5137</v>
+        <v>2.4892</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8749</v>
+        <v>1.8707</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4899</v>
+        <v>5.4363</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7926</v>
+        <v>2.7897</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6973</v>
+        <v>2.6466</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3197</v>
+        <v>4.0312</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3326</v>
+        <v>2.2634</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6973</v>
+        <v>2.6466</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0299</v>
+        <v>4.91</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2246</v>
+        <v>4.1429</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9344</v>
+        <v>1.897</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2989</v>
+        <v>1.2815</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2246</v>
+        <v>4.1429</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0755</v>
+        <v>3.1235</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1491</v>
+        <v>1.0194</v>
       </c>
       <c r="H6" t="n">
-        <v>5.253</v>
+        <v>5.2844</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8366</v>
+        <v>2.967</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1491</v>
+        <v>1.0194</v>
       </c>
       <c r="K6" t="n">
         <v>173</v>
@@ -713,7 +713,7 @@
         <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9857</v>
+        <v>3.9864</v>
       </c>
       <c r="N6" t="n">
         <v>254</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6423</v>
+        <v>3.497</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6677</v>
+        <v>1.6012</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0338</v>
+        <v>0.9873</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6423</v>
+        <v>3.497</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9837</v>
+        <v>3.8514</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3414</v>
+        <v>-0.3544</v>
       </c>
       <c r="H7" t="n">
-        <v>8.2494</v>
+        <v>8.0174</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4546</v>
+        <v>4.5015</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3414</v>
+        <v>-0.3544</v>
       </c>
       <c r="K7" t="n">
         <v>173</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1132</v>
+        <v>4.1471</v>
       </c>
       <c r="N7" t="n">
         <v>254</v>
@@ -768,127 +768,127 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.551</v>
+        <v>3.4407</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6259</v>
+        <v>1.5754</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9923</v>
+        <v>0.9616</v>
       </c>
       <c r="E8" t="n">
-        <v>3.551</v>
+        <v>3.4407</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6531</v>
+        <v>2.4699</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1021</v>
+        <v>0.9708</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1587</v>
+        <v>2.8306</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8657</v>
+        <v>1.5893</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1021</v>
+        <v>0.9708</v>
       </c>
       <c r="K8" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7636</v>
+        <v>2.5601</v>
       </c>
       <c r="N8" t="n">
-        <v>305</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5426</v>
+        <v>3.4294</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6221</v>
+        <v>1.5703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9885</v>
+        <v>0.9565</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5426</v>
+        <v>3.4294</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2534</v>
+        <v>3.5535</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2892</v>
+        <v>-0.1241</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2534</v>
+        <v>6.8986</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6768</v>
+        <v>3.8734</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2892</v>
+        <v>-0.1241</v>
       </c>
       <c r="K9" t="n">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="L9" t="n">
-        <v>232</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
-        <v>2.966</v>
+        <v>3.7493</v>
       </c>
       <c r="N9" t="n">
-        <v>430</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5418</v>
+        <v>3.2049</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6217</v>
+        <v>1.4675</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9881</v>
+        <v>0.8542</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5418</v>
+        <v>3.2049</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3639</v>
+        <v>1.0923</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1779</v>
+        <v>2.1126</v>
       </c>
       <c r="H10" t="n">
-        <v>2.905</v>
+        <v>1.0923</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5687</v>
+        <v>0.6133</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1779</v>
+        <v>2.1126</v>
       </c>
       <c r="K10" t="n">
         <v>198</v>
@@ -897,7 +897,7 @@
         <v>232</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7466</v>
+        <v>2.7259</v>
       </c>
       <c r="N10" t="n">
         <v>430</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2676</v>
+        <v>3.177</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4962</v>
+        <v>1.4547</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8633</v>
+        <v>0.8415</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2676</v>
+        <v>3.177</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2676</v>
+        <v>3.5969</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.4199</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4269</v>
+        <v>7.0617</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4269</v>
+        <v>3.965</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.4199</v>
       </c>
       <c r="K11" t="n">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4269</v>
+        <v>3.5451</v>
       </c>
       <c r="N11" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2537</v>
+        <v>3.1022</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4898</v>
+        <v>1.4204</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8569</v>
+        <v>0.8074</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2537</v>
+        <v>3.1022</v>
       </c>
       <c r="F12" t="n">
-        <v>3.66</v>
+        <v>3.1022</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4063</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7.1816</v>
+        <v>4.1591</v>
       </c>
       <c r="I12" t="n">
-        <v>3.878</v>
+        <v>4.1591</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4063</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4717</v>
+        <v>4.1591</v>
       </c>
       <c r="N12" t="n">
-        <v>254</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0421</v>
+        <v>3.0108</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3929</v>
+        <v>1.3786</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7658</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0421</v>
+        <v>3.0108</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7593</v>
+        <v>2.7596</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2828</v>
+        <v>0.2512</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2096</v>
+        <v>3.918</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2732</v>
+        <v>2.1998</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2828</v>
+        <v>0.2512</v>
       </c>
       <c r="K13" t="n">
         <v>242</v>
@@ -1035,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>2.556</v>
+        <v>2.451</v>
       </c>
       <c r="N13" t="n">
         <v>305</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9616</v>
+        <v>2.7943</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3561</v>
+        <v>1.2795</v>
       </c>
       <c r="D14" t="n">
-        <v>0.724</v>
+        <v>0.6671</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9616</v>
+        <v>2.7943</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9616</v>
+        <v>2.7943</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7571</v>
+        <v>3.4536</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7571</v>
+        <v>3.4536</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7571</v>
+        <v>3.4536</v>
       </c>
       <c r="N14" t="n">
         <v>241</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6386</v>
+        <v>2.6297</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2082</v>
+        <v>1.2041</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5769</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6386</v>
+        <v>2.6297</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2887</v>
+        <v>3.2287</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6501</v>
+        <v>-0.599</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9566</v>
+        <v>5.6792</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2165</v>
+        <v>3.1887</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6501</v>
+        <v>-0.599</v>
       </c>
       <c r="K15" t="n">
         <v>173</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5664</v>
+        <v>2.5897</v>
       </c>
       <c r="N15" t="n">
         <v>254</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5569</v>
+        <v>2.4748</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1708</v>
+        <v>1.1332</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5216</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5569</v>
+        <v>2.4748</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0339</v>
+        <v>2.9723</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.477</v>
+        <v>-0.4975</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1157</v>
+        <v>4.7168</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7625</v>
+        <v>2.6483</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.477</v>
+        <v>-0.4975</v>
       </c>
       <c r="K16" t="n">
         <v>173</v>
@@ -1173,7 +1173,7 @@
         <v>81</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2855</v>
+        <v>2.1508</v>
       </c>
       <c r="N16" t="n">
         <v>254</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.498</v>
+        <v>2.4147</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1438</v>
+        <v>1.1056</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5129</v>
+        <v>0.4942</v>
       </c>
       <c r="E17" t="n">
-        <v>2.498</v>
+        <v>2.4147</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9145</v>
+        <v>1.7823</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5835</v>
+        <v>0.6324</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9145</v>
+        <v>1.7823</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0338</v>
+        <v>1.0007</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5835</v>
+        <v>0.6324</v>
       </c>
       <c r="K17" t="n">
         <v>198</v>
@@ -1219,7 +1219,7 @@
         <v>232</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6173</v>
+        <v>1.6331</v>
       </c>
       <c r="N17" t="n">
         <v>430</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9569</v>
+        <v>2.0665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.896</v>
+        <v>0.9462</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2666</v>
+        <v>0.3356</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9569</v>
+        <v>2.0665</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1865</v>
+        <v>2.2812</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2296</v>
+        <v>-0.2147</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3199</v>
+        <v>2.2812</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2528</v>
+        <v>1.2808</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2296</v>
+        <v>-0.2147</v>
       </c>
       <c r="K18" t="n">
         <v>242</v>
@@ -1265,7 +1265,7 @@
         <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0232</v>
+        <v>1.0661</v>
       </c>
       <c r="N18" t="n">
         <v>305</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6506</v>
+        <v>0.5665</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0226</v>
+        <v>-0.0422</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4209</v>
+        <v>1.2372</v>
       </c>
       <c r="N19" t="n">
         <v>182</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5733</v>
+        <v>0.5343</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0542</v>
+        <v>-0.0742</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2521</v>
+        <v>1.167</v>
       </c>
       <c r="N20" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5523</v>
+        <v>0.5026</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0751</v>
+        <v>-0.1057</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2063</v>
+        <v>1.0977</v>
       </c>
       <c r="N21" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5341</v>
+        <v>0.4265</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1814</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1664</v>
+        <v>0.9315</v>
       </c>
       <c r="N22" t="n">
         <v>182</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3714</v>
+        <v>0.3159</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2549</v>
+        <v>-0.2915</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8112</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>172</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3679</v>
+        <v>0.3066</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2585</v>
+        <v>-0.3007</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8034</v>
+        <v>0.6697</v>
       </c>
       <c r="N24" t="n">
         <v>139</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1699</v>
+        <v>0.1639</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4553</v>
+        <v>-0.4427</v>
       </c>
       <c r="E25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="F25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="I25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.371</v>
+        <v>0.358</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0964</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5283</v>
+        <v>-0.5299</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2106</v>
+        <v>0.1666</v>
       </c>
       <c r="N26" t="n">
         <v>241</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0641</v>
+        <v>-0.0007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5605</v>
+        <v>-0.6065</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1399</v>
+        <v>-0.0015</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0232</v>
+        <v>-0.0595</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6011</v>
+        <v>-0.665</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0507</v>
+        <v>-0.1299</v>
       </c>
       <c r="N28" t="n">
         <v>241</v>
@@ -1734,216 +1734,216 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3181</v>
+        <v>-0.3511</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1457</v>
+        <v>-0.1608</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.769</v>
+        <v>-0.7657</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3181</v>
+        <v>-0.3511</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3181</v>
+        <v>-0.53</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.1789</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3181</v>
+        <v>-0.53</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3181</v>
+        <v>-0.2976</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1789</v>
       </c>
       <c r="K29" t="n">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3181</v>
+        <v>-0.1187</v>
       </c>
       <c r="N29" t="n">
-        <v>172</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1914</v>
+        <v>-0.1734</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8145</v>
+        <v>-0.7783</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.418</v>
+        <v>-0.3787</v>
       </c>
       <c r="N30" t="n">
-        <v>139</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2006</v>
+        <v>-0.175</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8237</v>
+        <v>-0.7799</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4382</v>
+        <v>-0.3821</v>
       </c>
       <c r="N31" t="n">
-        <v>241</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4483</v>
+        <v>-0.3938</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2053</v>
+        <v>-0.1803</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8283</v>
+        <v>-0.7852</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4483</v>
+        <v>-0.3938</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6535</v>
+        <v>-0.3938</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2052</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6535</v>
+        <v>-0.3938</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3529</v>
+        <v>-0.3938</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2052</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L32" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1477</v>
+        <v>-0.3938</v>
       </c>
       <c r="N32" t="n">
-        <v>430</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2384</v>
+        <v>-0.1887</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8612</v>
+        <v>-0.7936</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5206</v>
+        <v>-0.4122</v>
       </c>
       <c r="N33" t="n">
         <v>172</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.239</v>
+        <v>-0.2466</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8618</v>
+        <v>-0.8511</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5219</v>
+        <v>-0.5386</v>
       </c>
       <c r="N34" t="n">
         <v>182</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3211</v>
+        <v>-0.3264</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9434</v>
+        <v>-0.9305</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7012</v>
+        <v>-0.7129</v>
       </c>
       <c r="N35" t="n">
         <v>182</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4131</v>
+        <v>-0.403</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0349</v>
+        <v>-1.0067</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9023</v>
+        <v>-0.8801</v>
       </c>
       <c r="N36" t="n">
         <v>139</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9866</v>
+        <v>-0.9055</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4517</v>
+        <v>-0.4146</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0733</v>
+        <v>-1.0183</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9866</v>
+        <v>-0.9055</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6433</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3433</v>
+        <v>-0.3344</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6433</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3474</v>
+        <v>-0.3206</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3433</v>
+        <v>-0.3344</v>
       </c>
       <c r="K37" t="n">
         <v>242</v>
@@ -2139,7 +2139,7 @@
         <v>63</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6907</v>
+        <v>-0.655</v>
       </c>
       <c r="N37" t="n">
         <v>305</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1902</v>
+        <v>-1.0863</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.545</v>
+        <v>-0.4974</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.166</v>
+        <v>-1.1006</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1902</v>
+        <v>-1.0863</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.008</v>
+        <v>-1.0863</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.1822</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.008</v>
+        <v>-1.0863</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0043</v>
+        <v>-1.0863</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.1822</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L38" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1865</v>
+        <v>-1.0863</v>
       </c>
       <c r="N38" t="n">
-        <v>323</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2069</v>
+        <v>-1.2569</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5526</v>
+        <v>-0.5755</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1736</v>
+        <v>-1.1784</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2069</v>
+        <v>-1.2569</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2069</v>
+        <v>-0.0864</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-1.1705</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2069</v>
+        <v>-0.0864</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2069</v>
+        <v>-0.0485</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-1.1705</v>
       </c>
       <c r="K39" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2069</v>
+        <v>-1.219</v>
       </c>
       <c r="N39" t="n">
-        <v>172</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9593</v>
+        <v>-1.9643</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8971</v>
+        <v>-0.8994</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5161</v>
+        <v>-1.5006</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9593</v>
+        <v>-1.9643</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.156</v>
+        <v>-3.0563</v>
       </c>
       <c r="G40" t="n">
-        <v>1.1967</v>
+        <v>1.092</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.156</v>
+        <v>-3.0563</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7042</v>
+        <v>-1.716</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1967</v>
+        <v>1.092</v>
       </c>
       <c r="K40" t="n">
         <v>198</v>
@@ -2277,7 +2277,7 @@
         <v>232</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.5074999999999998</v>
+        <v>-0.6239999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>430</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2489</v>
+        <v>-3.0367</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4876</v>
+        <v>-1.3904</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1032</v>
+        <v>-1.9891</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2489</v>
+        <v>-3.0367</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2676</v>
+        <v>-3.0292</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0187</v>
+        <v>-0.0075</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2676</v>
+        <v>-3.0292</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7644</v>
+        <v>-1.7008</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0187</v>
+        <v>-0.0075</v>
       </c>
       <c r="K41" t="n">
         <v>242</v>
@@ -2323,7 +2323,7 @@
         <v>63</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7457</v>
+        <v>-1.7083</v>
       </c>
       <c r="N41" t="n">
         <v>305</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3813</v>
+        <v>0.38</v>
       </c>
       <c r="J2" t="n">
-        <v>9.9138</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1708</v>
+        <v>0.1544</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4408</v>
+        <v>4.0144</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.74</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2986</v>
+        <v>-0.2806</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.7636</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.336</v>
+        <v>-0.3198</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.736000000000001</v>
+        <v>-8.3148</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3635</v>
+        <v>-0.3492</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.451000000000001</v>
+        <v>-9.0792</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9014</v>
+        <v>0.834</v>
       </c>
       <c r="J7" t="n">
-        <v>23.4364</v>
+        <v>21.684</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5994</v>
+        <v>0.5283</v>
       </c>
       <c r="J8" t="n">
-        <v>15.5844</v>
+        <v>13.7358</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.24</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3431</v>
+        <v>0.2871</v>
       </c>
       <c r="J9" t="n">
-        <v>8.9206</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1177</v>
+        <v>-0.1003</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0602</v>
+        <v>-2.6078</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.338</v>
+        <v>-0.325</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.788</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1396</v>
+        <v>1.1496</v>
       </c>
       <c r="J12" t="n">
-        <v>25.0712</v>
+        <v>25.2912</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.42</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9586</v>
+        <v>0.952</v>
       </c>
       <c r="J13" t="n">
-        <v>21.0892</v>
+        <v>20.944</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7729</v>
+        <v>0.7542</v>
       </c>
       <c r="J14" t="n">
-        <v>17.0038</v>
+        <v>16.5924</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6324</v>
+        <v>0.6072</v>
       </c>
       <c r="J15" t="n">
-        <v>13.9128</v>
+        <v>13.3584</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5854</v>
       </c>
       <c r="J16" t="n">
-        <v>13.4508</v>
+        <v>12.8788</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.99</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0098</v>
+        <v>0.0186</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2156</v>
+        <v>0.4092</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.83</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2006</v>
+        <v>-0.1846</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.4132</v>
+        <v>-4.0612</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.221</v>
+        <v>-0.2049</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.862</v>
+        <v>-4.5078</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.65</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3685</v>
+        <v>-0.3549</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.106999999999999</v>
+        <v>-7.8078</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4838</v>
+        <v>-0.4805</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.6436</v>
+        <v>-10.571</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9342</v>
+        <v>0.9193</v>
       </c>
       <c r="J22" t="n">
-        <v>32.697</v>
+        <v>32.1755</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5798</v>
+        <v>0.5422</v>
       </c>
       <c r="J23" t="n">
-        <v>20.293</v>
+        <v>18.977</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5352</v>
+        <v>0.4966</v>
       </c>
       <c r="J24" t="n">
-        <v>18.732</v>
+        <v>17.381</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3102</v>
+        <v>-0.2689</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.857</v>
+        <v>-9.4115</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.417</v>
+        <v>-0.3744</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.595</v>
+        <v>-13.104</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2379</v>
+        <v>0.1925</v>
       </c>
       <c r="J27" t="n">
-        <v>8.326499999999999</v>
+        <v>6.7375</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.07</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1964</v>
+        <v>0.1555</v>
       </c>
       <c r="J28" t="n">
-        <v>6.874</v>
+        <v>5.4425</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1288</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>4.508</v>
+        <v>3.3985</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0707</v>
+        <v>-0.0571</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.4745</v>
+        <v>-1.9985</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3452</v>
+        <v>-0.33</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.082</v>
+        <v>-11.55</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.33</v>
       </c>
       <c r="I32" t="n">
-        <v>0.496</v>
+        <v>0.5047</v>
       </c>
       <c r="J32" t="n">
-        <v>13.888</v>
+        <v>14.1316</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2927</v>
+        <v>0.2803</v>
       </c>
       <c r="J33" t="n">
-        <v>8.195600000000001</v>
+        <v>7.8484</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1292</v>
+        <v>0.114</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6176</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.92</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.127</v>
+        <v>-0.108</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.556</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3326</v>
+        <v>-0.3171</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.312799999999999</v>
+        <v>-8.8788</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7048</v>
+        <v>0.6335</v>
       </c>
       <c r="J37" t="n">
-        <v>19.7344</v>
+        <v>17.738</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.34</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4632</v>
+        <v>0.3966</v>
       </c>
       <c r="J38" t="n">
-        <v>12.9696</v>
+        <v>11.1048</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0975</v>
+        <v>0.0727</v>
       </c>
       <c r="J39" t="n">
-        <v>2.73</v>
+        <v>2.0356</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.124</v>
+        <v>-0.1054</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.472</v>
+        <v>-2.9512</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.193</v>
+        <v>-0.1729</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.404</v>
+        <v>-4.8412</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1003</v>
+        <v>1.1034</v>
       </c>
       <c r="J42" t="n">
-        <v>44.012</v>
+        <v>44.136</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6606</v>
+        <v>0.6268</v>
       </c>
       <c r="J43" t="n">
-        <v>26.424</v>
+        <v>25.072</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4855</v>
+        <v>0.4479</v>
       </c>
       <c r="J44" t="n">
-        <v>19.42</v>
+        <v>17.916</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.11</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3445</v>
+        <v>0.3089</v>
       </c>
       <c r="J45" t="n">
-        <v>13.78</v>
+        <v>12.356</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7932</v>
+        <v>-0.7706</v>
       </c>
       <c r="J46" t="n">
-        <v>-31.728</v>
+        <v>-30.824</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5556</v>
       </c>
       <c r="J47" t="n">
-        <v>24.416</v>
+        <v>22.224</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0129</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>0.516</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1933</v>
+        <v>-0.1736</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.732</v>
+        <v>-6.944</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.33</v>
+        <v>-0.3135</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.2</v>
+        <v>-12.54</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3392</v>
+        <v>-0.3233</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.568</v>
+        <v>-12.932</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.479</v>
+        <v>0.4114</v>
       </c>
       <c r="J52" t="n">
-        <v>14.37</v>
+        <v>12.342</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3653</v>
+        <v>0.3047</v>
       </c>
       <c r="J53" t="n">
-        <v>10.959</v>
+        <v>9.141</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3535</v>
+        <v>0.2939</v>
       </c>
       <c r="J54" t="n">
-        <v>10.605</v>
+        <v>8.817</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1478</v>
+        <v>0.1138</v>
       </c>
       <c r="J55" t="n">
-        <v>4.434</v>
+        <v>3.414</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3756</v>
+        <v>-0.3644</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.268</v>
+        <v>-10.932</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.36</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5523</v>
+        <v>0.5725</v>
       </c>
       <c r="J57" t="n">
-        <v>16.569</v>
+        <v>17.175</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.25</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4146</v>
+        <v>0.4142</v>
       </c>
       <c r="J58" t="n">
-        <v>12.438</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2182</v>
+        <v>-0.1978</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.546</v>
+        <v>-5.934</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3529</v>
+        <v>-0.3381</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.587</v>
+        <v>-10.143</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3891</v>
+        <v>-0.3774</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.673</v>
+        <v>-11.322</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8395</v>
+        <v>0.7882</v>
       </c>
       <c r="J62" t="n">
-        <v>25.185</v>
+        <v>23.646</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1853</v>
+        <v>0.1475</v>
       </c>
       <c r="J63" t="n">
-        <v>5.559</v>
+        <v>4.425</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0283</v>
+        <v>-0.0201</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.849</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1622</v>
+        <v>-0.1419</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.866</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2465</v>
+        <v>-0.2266</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.395</v>
+        <v>-6.798</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0184</v>
+        <v>1.0197</v>
       </c>
       <c r="J67" t="n">
-        <v>30.552</v>
+        <v>30.591</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6562</v>
+        <v>0.6203</v>
       </c>
       <c r="J68" t="n">
-        <v>19.686</v>
+        <v>18.609</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2481</v>
+        <v>0.2135</v>
       </c>
       <c r="J69" t="n">
-        <v>7.443</v>
+        <v>6.405</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4589</v>
+        <v>-0.4163</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.767</v>
+        <v>-12.489</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6703</v>
+        <v>-0.6363</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.109</v>
+        <v>-19.089</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7825</v>
+        <v>0.7328</v>
       </c>
       <c r="J72" t="n">
-        <v>21.1275</v>
+        <v>19.7856</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.06</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1782</v>
+        <v>0.1393</v>
       </c>
       <c r="J73" t="n">
-        <v>4.8114</v>
+        <v>3.7611</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0799</v>
+        <v>0.0567</v>
       </c>
       <c r="J74" t="n">
-        <v>2.1573</v>
+        <v>1.5309</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3799</v>
+        <v>-0.3674</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.2573</v>
+        <v>-9.9198</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4157</v>
+        <v>-0.4066</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.2239</v>
+        <v>-10.9782</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>1.129</v>
+        <v>1.1414</v>
       </c>
       <c r="J77" t="n">
-        <v>30.483</v>
+        <v>30.8178</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>1.074</v>
+        <v>1.0828</v>
       </c>
       <c r="J78" t="n">
-        <v>28.998</v>
+        <v>29.2356</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.14</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4081</v>
+        <v>0.3741</v>
       </c>
       <c r="J79" t="n">
-        <v>11.0187</v>
+        <v>10.1007</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3083</v>
+        <v>0.2758</v>
       </c>
       <c r="J80" t="n">
-        <v>8.3241</v>
+        <v>7.4466</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.581</v>
+        <v>-0.5451</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.687</v>
+        <v>-14.7177</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.197</v>
+        <v>0.1608</v>
       </c>
       <c r="J82" t="n">
-        <v>4.925</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1174</v>
+        <v>-0.1028</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.935</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2152</v>
+        <v>-0.198</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.38</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.72</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3091</v>
+        <v>-0.2923</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.7275</v>
+        <v>-7.3075</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5056</v>
+        <v>-0.5054</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.64</v>
+        <v>-12.635</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1237</v>
+        <v>1.1164</v>
       </c>
       <c r="J87" t="n">
-        <v>28.0925</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9906</v>
+        <v>0.9777</v>
       </c>
       <c r="J88" t="n">
-        <v>24.765</v>
+        <v>24.4425</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.37</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7685</v>
+        <v>0.7539</v>
       </c>
       <c r="J89" t="n">
-        <v>19.2125</v>
+        <v>18.8475</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1408</v>
+        <v>-0.1139</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.52</v>
+        <v>-2.8475</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.66</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9333</v>
+        <v>-0.9282</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.3325</v>
+        <v>-23.205</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4927</v>
+        <v>0.443</v>
       </c>
       <c r="J92" t="n">
-        <v>14.781</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.243</v>
+        <v>0.195</v>
       </c>
       <c r="J93" t="n">
-        <v>7.29</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.204</v>
+        <v>0.1613</v>
       </c>
       <c r="J94" t="n">
-        <v>6.12</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1625</v>
+        <v>0.1261</v>
       </c>
       <c r="J95" t="n">
-        <v>4.875</v>
+        <v>3.783</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2012</v>
+        <v>-0.1809</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.036</v>
+        <v>-5.427</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2007</v>
+        <v>0.1839</v>
       </c>
       <c r="J97" t="n">
-        <v>6.021</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1691</v>
+        <v>0.152</v>
       </c>
       <c r="J98" t="n">
-        <v>5.073</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0711</v>
+        <v>-0.0574</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.133</v>
+        <v>-1.722</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1675</v>
+        <v>-0.1474</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.025</v>
+        <v>-4.422</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.88</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1675</v>
+        <v>-0.1474</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.025</v>
+        <v>-4.422</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4594</v>
+        <v>0.4156</v>
       </c>
       <c r="J102" t="n">
-        <v>11.9444</v>
+        <v>10.8056</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.9</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1339</v>
+        <v>-0.1182</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.4814</v>
+        <v>-3.0732</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2753</v>
+        <v>-0.2571</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.1578</v>
+        <v>-6.6846</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3315</v>
+        <v>-0.3153</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.619</v>
+        <v>-8.197800000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3951</v>
+        <v>-0.3832</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.2726</v>
+        <v>-9.963200000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.47</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9107</v>
+        <v>0.896</v>
       </c>
       <c r="J107" t="n">
-        <v>23.6782</v>
+        <v>23.296</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.623</v>
+        <v>0.6128</v>
       </c>
       <c r="J108" t="n">
-        <v>16.198</v>
+        <v>15.9328</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5471</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>14.2246</v>
+        <v>14.0608</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3821</v>
+        <v>0.3486</v>
       </c>
       <c r="J110" t="n">
-        <v>9.9346</v>
+        <v>9.063599999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>0.0796</v>
       </c>
       <c r="J111" t="n">
-        <v>2.6</v>
+        <v>2.0696</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6869</v>
+        <v>0.6732</v>
       </c>
       <c r="J112" t="n">
-        <v>18.5463</v>
+        <v>18.1764</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6113</v>
+        <v>0.6006</v>
       </c>
       <c r="J113" t="n">
-        <v>16.5051</v>
+        <v>16.2162</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.16</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4517</v>
+        <v>0.4227</v>
       </c>
       <c r="J114" t="n">
-        <v>12.1959</v>
+        <v>11.4129</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3867</v>
+        <v>0.3523</v>
       </c>
       <c r="J115" t="n">
-        <v>10.4409</v>
+        <v>9.5121</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.11</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3369</v>
+        <v>0.3034</v>
       </c>
       <c r="J116" t="n">
-        <v>9.096299999999999</v>
+        <v>8.191800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.06</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1953</v>
+        <v>0.1551</v>
       </c>
       <c r="J117" t="n">
-        <v>5.2731</v>
+        <v>4.1877</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0193</v>
+        <v>0.0142</v>
       </c>
       <c r="J118" t="n">
-        <v>0.5211</v>
+        <v>0.3834</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0193</v>
+        <v>0.0142</v>
       </c>
       <c r="J119" t="n">
-        <v>0.5211</v>
+        <v>0.3834</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2212</v>
+        <v>-0.2017</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.9724</v>
+        <v>-5.4459</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.52</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4961</v>
+        <v>-0.4957</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.3947</v>
+        <v>-13.3839</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1871</v>
+        <v>1.186</v>
       </c>
       <c r="J122" t="n">
-        <v>42.7356</v>
+        <v>42.696</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.26</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6181</v>
+        <v>0.6057</v>
       </c>
       <c r="J123" t="n">
-        <v>22.2516</v>
+        <v>21.8052</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2377</v>
+        <v>0.2066</v>
       </c>
       <c r="J124" t="n">
-        <v>8.5572</v>
+        <v>7.4376</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0771</v>
+        <v>0.0605</v>
       </c>
       <c r="J125" t="n">
-        <v>2.7756</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.72</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7935</v>
+        <v>-0.7711</v>
       </c>
       <c r="J126" t="n">
-        <v>-28.566</v>
+        <v>-27.7596</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.49</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7789</v>
+        <v>0.7469</v>
       </c>
       <c r="J127" t="n">
-        <v>28.0404</v>
+        <v>26.8884</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2399</v>
+        <v>0.1942</v>
       </c>
       <c r="J128" t="n">
-        <v>8.6364</v>
+        <v>6.9912</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2489</v>
+        <v>-0.2289</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.9604</v>
+        <v>-8.240399999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2974</v>
+        <v>-0.2792</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.7064</v>
+        <v>-10.0512</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3626</v>
+        <v>-0.3486</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.0536</v>
+        <v>-12.5496</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.88</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6379</v>
+        <v>1.6963</v>
       </c>
       <c r="J132" t="n">
-        <v>44.2233</v>
+        <v>45.8001</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5828</v>
+        <v>0.5447</v>
       </c>
       <c r="J133" t="n">
-        <v>15.7356</v>
+        <v>14.7069</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5376</v>
+        <v>-0.4974</v>
       </c>
       <c r="J134" t="n">
-        <v>-14.5152</v>
+        <v>-13.4298</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.82</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5613</v>
+        <v>-0.522</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.1551</v>
+        <v>-14.094</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.676</v>
+        <v>-0.643</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.252</v>
+        <v>-17.361</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.27</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5454</v>
+        <v>0.4859</v>
       </c>
       <c r="J137" t="n">
-        <v>14.7258</v>
+        <v>13.1193</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3249</v>
+        <v>0.2727</v>
       </c>
       <c r="J138" t="n">
-        <v>8.7723</v>
+        <v>7.3629</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.11</v>
       </c>
       <c r="I139" t="n">
-        <v>0.269</v>
+        <v>0.2212</v>
       </c>
       <c r="J139" t="n">
-        <v>7.263</v>
+        <v>5.9724</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1816</v>
+        <v>-0.161</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.9032</v>
+        <v>-4.347</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3582</v>
+        <v>-0.3444</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.6714</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0255</v>
+        <v>1.0268</v>
       </c>
       <c r="J142" t="n">
-        <v>24.612</v>
+        <v>24.6432</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7808</v>
+        <v>0.754</v>
       </c>
       <c r="J143" t="n">
-        <v>18.7392</v>
+        <v>18.096</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.391</v>
+        <v>0.3553</v>
       </c>
       <c r="J144" t="n">
-        <v>9.384</v>
+        <v>8.527200000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.066</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.088</v>
+        <v>-1.584</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.95</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2308</v>
+        <v>-0.1939</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.5392</v>
+        <v>-4.6536</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.3</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6208</v>
+        <v>0.5654</v>
       </c>
       <c r="J147" t="n">
-        <v>14.8992</v>
+        <v>13.5696</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.152</v>
+        <v>-0.1332</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.648</v>
+        <v>-3.1968</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.82</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2255</v>
+        <v>-0.2054</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.412</v>
+        <v>-4.9296</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.82</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2255</v>
+        <v>-0.2054</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.412</v>
+        <v>-4.9296</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.8</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2455</v>
+        <v>-0.2256</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.892</v>
+        <v>-5.4144</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2421</v>
+        <v>-0.228</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.3578</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3383</v>
+        <v>-0.3273</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.0894</v>
+        <v>-5.8914</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3641</v>
+        <v>-0.3536</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.5538</v>
+        <v>-6.3648</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3984</v>
+        <v>-0.3888</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.1712</v>
+        <v>-6.9984</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.53</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4598</v>
+        <v>-0.454</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.276400000000001</v>
+        <v>-8.172000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.75</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8216</v>
+        <v>0.7517</v>
       </c>
       <c r="J157" t="n">
-        <v>14.7888</v>
+        <v>13.5306</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7405</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>13.329</v>
+        <v>12.0762</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.52</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6121</v>
+        <v>0.546</v>
       </c>
       <c r="J159" t="n">
-        <v>11.0178</v>
+        <v>9.827999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5454</v>
+        <v>0.4821</v>
       </c>
       <c r="J160" t="n">
-        <v>9.8172</v>
+        <v>8.6778</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.24</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3217</v>
+        <v>0.271</v>
       </c>
       <c r="J161" t="n">
-        <v>5.7906</v>
+        <v>4.878</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.699</v>
+        <v>0.6654</v>
       </c>
       <c r="J162" t="n">
-        <v>18.873</v>
+        <v>17.9658</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.1</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3273</v>
+        <v>0.2887</v>
       </c>
       <c r="J163" t="n">
-        <v>8.8371</v>
+        <v>7.7949</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.09</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3013</v>
+        <v>0.2638</v>
       </c>
       <c r="J164" t="n">
-        <v>8.1351</v>
+        <v>7.1226</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0111</v>
+        <v>-0.0073</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.2997</v>
+        <v>-0.1971</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3021</v>
+        <v>-0.2608</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.156700000000001</v>
+        <v>-7.0416</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9246</v>
+        <v>0.8823</v>
       </c>
       <c r="J167" t="n">
-        <v>24.9642</v>
+        <v>23.8221</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4493</v>
+        <v>0.3912</v>
       </c>
       <c r="J168" t="n">
-        <v>12.1311</v>
+        <v>10.5624</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.202</v>
+        <v>-0.1814</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.454</v>
+        <v>-4.8978</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2329</v>
+        <v>-0.2126</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.2883</v>
+        <v>-5.7402</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4113</v>
+        <v>-0.4023</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.1051</v>
+        <v>-10.8621</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7109</v>
+        <v>0.678</v>
       </c>
       <c r="J172" t="n">
-        <v>20.6161</v>
+        <v>19.662</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.19</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5543</v>
+        <v>0.5138</v>
       </c>
       <c r="J173" t="n">
-        <v>16.0747</v>
+        <v>14.9002</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1637</v>
+        <v>0.1342</v>
       </c>
       <c r="J174" t="n">
-        <v>4.7473</v>
+        <v>3.8918</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2065</v>
+        <v>-0.1708</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.9885</v>
+        <v>-4.9532</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7512</v>
+        <v>-0.7224</v>
       </c>
       <c r="J176" t="n">
-        <v>-21.7848</v>
+        <v>-20.9496</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.28</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5451</v>
+        <v>0.4854</v>
       </c>
       <c r="J177" t="n">
-        <v>15.8079</v>
+        <v>14.0766</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4164</v>
+        <v>0.3603</v>
       </c>
       <c r="J178" t="n">
-        <v>12.0756</v>
+        <v>10.4487</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2404</v>
+        <v>0.1975</v>
       </c>
       <c r="J179" t="n">
-        <v>6.9716</v>
+        <v>5.7275</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.093</v>
+        <v>-0.0762</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.697</v>
+        <v>-2.2098</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1543</v>
+        <v>-0.1342</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.4747</v>
+        <v>-3.8918</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.94</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5807</v>
+        <v>1.619</v>
       </c>
       <c r="J182" t="n">
-        <v>26.8719</v>
+        <v>27.523</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.85</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4766</v>
+        <v>1.5084</v>
       </c>
       <c r="J183" t="n">
-        <v>25.1022</v>
+        <v>25.6428</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.61</v>
       </c>
       <c r="I184" t="n">
-        <v>1.1919</v>
+        <v>1.2141</v>
       </c>
       <c r="J184" t="n">
-        <v>20.2623</v>
+        <v>20.6397</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.33</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7587</v>
+        <v>0.7458</v>
       </c>
       <c r="J185" t="n">
-        <v>12.8979</v>
+        <v>12.6786</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.3</v>
       </c>
       <c r="I186" t="n">
-        <v>0.6992</v>
+        <v>0.6817</v>
       </c>
       <c r="J186" t="n">
-        <v>11.8864</v>
+        <v>11.5889</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0032</v>
+        <v>0.0524</v>
       </c>
       <c r="J187" t="n">
-        <v>-0.0544</v>
+        <v>0.8908</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.4215</v>
+        <v>-0.4169</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.1655</v>
+        <v>-7.0873</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.5</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4715</v>
+        <v>-0.4686</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.015499999999999</v>
+        <v>-7.9662</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5507</v>
+        <v>-0.5547</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.3619</v>
+        <v>-9.4299</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.31</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6402</v>
+        <v>-0.6576</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.8834</v>
+        <v>-11.1792</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.91</v>
       </c>
       <c r="I192" t="n">
-        <v>1.56</v>
+        <v>1.596</v>
       </c>
       <c r="J192" t="n">
-        <v>31.2</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.71</v>
       </c>
       <c r="I193" t="n">
-        <v>1.3214</v>
+        <v>1.3442</v>
       </c>
       <c r="J193" t="n">
-        <v>26.428</v>
+        <v>26.884</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1615</v>
+        <v>1.1804</v>
       </c>
       <c r="J194" t="n">
-        <v>23.23</v>
+        <v>23.608</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.37</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8476</v>
+        <v>0.8401</v>
       </c>
       <c r="J195" t="n">
-        <v>16.952</v>
+        <v>16.802</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.02</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0185</v>
+        <v>-0.0032</v>
       </c>
       <c r="J196" t="n">
-        <v>0.37</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.96</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0286</v>
+        <v>0.0774</v>
       </c>
       <c r="J197" t="n">
-        <v>0.572</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.63</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3627</v>
+        <v>-0.3551</v>
       </c>
       <c r="J198" t="n">
-        <v>-7.254</v>
+        <v>-7.102</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4488</v>
+        <v>-0.444</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.976000000000001</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.37</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5899</v>
+        <v>-0.5992</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.798</v>
+        <v>-11.984</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.34</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6166</v>
+        <v>-0.6302</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.332</v>
+        <v>-12.604</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.063</v>
+        <v>-0.051</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.449</v>
+        <v>-1.173</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.86</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1718</v>
+        <v>-0.1558</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.9514</v>
+        <v>-3.5834</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2134</v>
+        <v>-0.1968</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.9082</v>
+        <v>-4.5264</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3347</v>
+        <v>-0.3192</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.6981</v>
+        <v>-7.3416</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4247</v>
+        <v>-0.4153</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.7681</v>
+        <v>-9.5519</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.69</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7869</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>18.0987</v>
+        <v>16.4496</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6148</v>
+        <v>0.5448</v>
       </c>
       <c r="J208" t="n">
-        <v>14.1404</v>
+        <v>12.5304</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.39</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4952</v>
+        <v>0.4306</v>
       </c>
       <c r="J209" t="n">
-        <v>11.3896</v>
+        <v>9.9038</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.21</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2996</v>
+        <v>0.2499</v>
       </c>
       <c r="J210" t="n">
-        <v>6.8908</v>
+        <v>5.7477</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.587</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.29</v>
       </c>
       <c r="I212" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J212" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>2.14</v>
       </c>
       <c r="I213" t="n">
-        <v>1.7983</v>
+        <v>1.855</v>
       </c>
       <c r="J213" t="n">
-        <v>32.3694</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.52</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0765</v>
+        <v>1.0978</v>
       </c>
       <c r="J214" t="n">
-        <v>19.377</v>
+        <v>19.7604</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6317</v>
+        <v>0.6093</v>
       </c>
       <c r="J215" t="n">
-        <v>11.3706</v>
+        <v>10.9674</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.06</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1329</v>
+        <v>0.0974</v>
       </c>
       <c r="J216" t="n">
-        <v>2.3922</v>
+        <v>1.7532</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2367</v>
+        <v>-0.2159</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.2606</v>
+        <v>-3.8862</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.59</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3821</v>
+        <v>-0.3772</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.8778</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4107</v>
+        <v>-0.4079</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.3926</v>
+        <v>-7.3422</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.31</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6314</v>
+        <v>-0.6464</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.3652</v>
+        <v>-11.6352</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.25</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6866</v>
+        <v>-0.7118</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.3588</v>
+        <v>-12.8124</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8396</v>
+        <v>0.8206</v>
       </c>
       <c r="J222" t="n">
-        <v>20.1504</v>
+        <v>19.6944</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8008</v>
+        <v>0.7794</v>
       </c>
       <c r="J223" t="n">
-        <v>19.2192</v>
+        <v>18.7056</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.31</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7617</v>
+        <v>0.7382</v>
       </c>
       <c r="J224" t="n">
-        <v>18.2808</v>
+        <v>17.7168</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7026</v>
+        <v>0.6765</v>
       </c>
       <c r="J225" t="n">
-        <v>16.8624</v>
+        <v>16.236</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.07</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2173</v>
+        <v>0.1881</v>
       </c>
       <c r="J226" t="n">
-        <v>5.2152</v>
+        <v>4.5144</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.21</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5065</v>
+        <v>0.4559</v>
       </c>
       <c r="J227" t="n">
-        <v>12.156</v>
+        <v>10.9416</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.08</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2553</v>
+        <v>0.2118</v>
       </c>
       <c r="J228" t="n">
-        <v>6.1272</v>
+        <v>5.0832</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2169</v>
+        <v>-0.1988</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.2056</v>
+        <v>-4.7712</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3763</v>
+        <v>-0.3629</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.0312</v>
+        <v>-8.7096</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.6496</v>
+        <v>-15.0456</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.59</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2196</v>
+        <v>1.2353</v>
       </c>
       <c r="J232" t="n">
-        <v>32.9292</v>
+        <v>33.3531</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.33</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8076</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>21.8052</v>
+        <v>21.1896</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.32</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="J234" t="n">
-        <v>21.2706</v>
+        <v>20.6226</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0384</v>
+        <v>-0.033</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.0368</v>
+        <v>-0.891</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.385</v>
+        <v>-0.3446</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.395</v>
+        <v>-9.3042</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.17</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3976</v>
+        <v>0.3421</v>
       </c>
       <c r="J237" t="n">
-        <v>10.7352</v>
+        <v>9.236700000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1303</v>
+        <v>-0.1124</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.5181</v>
+        <v>-3.0348</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1416</v>
+        <v>-0.1231</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.8232</v>
+        <v>-3.3237</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1416</v>
+        <v>-0.1231</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.8232</v>
+        <v>-3.3237</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2464</v>
+        <v>-0.2265</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.6528</v>
+        <v>-6.1155</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.63</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3028</v>
+        <v>1.3262</v>
       </c>
       <c r="J242" t="n">
-        <v>36.4784</v>
+        <v>37.1336</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7088</v>
+        <v>0.6765</v>
       </c>
       <c r="J243" t="n">
-        <v>19.8464</v>
+        <v>18.942</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0189</v>
+        <v>-0.014</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.5292</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.85</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4924</v>
+        <v>-0.451</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.7872</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5167</v>
+        <v>-0.476</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.4676</v>
+        <v>-13.328</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7299</v>
+        <v>0.6741</v>
       </c>
       <c r="J247" t="n">
-        <v>20.4372</v>
+        <v>18.8748</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.17</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3776</v>
+        <v>0.3223</v>
       </c>
       <c r="J248" t="n">
-        <v>10.5728</v>
+        <v>9.0244</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.95</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0876</v>
+        <v>-0.0716</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.4528</v>
+        <v>-2.0048</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2542</v>
+        <v>-0.2344</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.1176</v>
+        <v>-6.5632</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.3948</v>
+        <v>-6.8516</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9678</v>
+        <v>0.9615</v>
       </c>
       <c r="J252" t="n">
-        <v>21.2916</v>
+        <v>21.153</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.42</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9678</v>
+        <v>0.9615</v>
       </c>
       <c r="J253" t="n">
-        <v>21.2916</v>
+        <v>21.153</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.35</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8377</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>18.4294</v>
+        <v>18.0202</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.19</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5133</v>
+        <v>0.4822</v>
       </c>
       <c r="J255" t="n">
-        <v>11.2926</v>
+        <v>10.6084</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.02</v>
       </c>
       <c r="I256" t="n">
-        <v>0.054</v>
+        <v>0.0375</v>
       </c>
       <c r="J256" t="n">
-        <v>1.188</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.08</v>
       </c>
       <c r="I257" t="n">
-        <v>0.25</v>
+        <v>0.206</v>
       </c>
       <c r="J257" t="n">
-        <v>5.5</v>
+        <v>4.532</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.96</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0588</v>
+        <v>-0.048</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.2936</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1572</v>
+        <v>-0.1403</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.4584</v>
+        <v>-3.0866</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.4922</v>
+        <v>-6.0984</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4579</v>
+        <v>-0.4524</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.0738</v>
+        <v>-9.9528</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.57</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7659</v>
+        <v>0.8232</v>
       </c>
       <c r="J262" t="n">
-        <v>22.2111</v>
+        <v>23.8728</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2348</v>
+        <v>0.2201</v>
       </c>
       <c r="J263" t="n">
-        <v>6.8092</v>
+        <v>6.3829</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0034</v>
+        <v>-0.0021</v>
       </c>
       <c r="J264" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0609</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2169</v>
+        <v>-0.1964</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.2901</v>
+        <v>-5.6956</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3153</v>
+        <v>-0.2987</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.143700000000001</v>
+        <v>-8.6623</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2647</v>
+        <v>0.2126</v>
       </c>
       <c r="J267" t="n">
-        <v>7.6763</v>
+        <v>6.1654</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1534</v>
+        <v>0.1166</v>
       </c>
       <c r="J268" t="n">
-        <v>4.4486</v>
+        <v>3.3814</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.052</v>
+        <v>0.0358</v>
       </c>
       <c r="J269" t="n">
-        <v>1.508</v>
+        <v>1.0382</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0455</v>
+        <v>-0.0343</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.3195</v>
+        <v>-0.9947</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0756</v>
+        <v>-0.0605</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.1924</v>
+        <v>-1.7545</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6641</v>
+        <v>0.6283</v>
       </c>
       <c r="J272" t="n">
-        <v>19.2589</v>
+        <v>18.2207</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.04</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1629</v>
+        <v>0.134</v>
       </c>
       <c r="J273" t="n">
-        <v>4.7241</v>
+        <v>3.886</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.02</v>
       </c>
       <c r="I274" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="J274" t="n">
-        <v>2.7347</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0534</v>
+        <v>0.04</v>
       </c>
       <c r="J275" t="n">
-        <v>1.5486</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3238</v>
+        <v>-0.2819</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.3902</v>
+        <v>-8.1751</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6029</v>
+        <v>0.5433</v>
       </c>
       <c r="J277" t="n">
-        <v>17.4841</v>
+        <v>15.7557</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3209</v>
+        <v>0.2694</v>
       </c>
       <c r="J278" t="n">
-        <v>9.306100000000001</v>
+        <v>7.8126</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2463</v>
+        <v>0.2012</v>
       </c>
       <c r="J279" t="n">
-        <v>7.1427</v>
+        <v>5.8348</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.83</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2256</v>
+        <v>-0.2052</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.5424</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2458</v>
+        <v>-0.2259</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.1282</v>
+        <v>-6.5511</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.1866</v>
+        <v>0.1695</v>
       </c>
       <c r="J282" t="n">
-        <v>5.598</v>
+        <v>5.085</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0023</v>
+        <v>0.0013</v>
       </c>
       <c r="J283" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.99</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0238</v>
+        <v>-0.0175</v>
       </c>
       <c r="J284" t="n">
-        <v>-0.714</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.97</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0565</v>
+        <v>-0.0448</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.695</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2497</v>
+        <v>-0.2297</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.491</v>
+        <v>-6.891</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6586</v>
+        <v>0.5873</v>
       </c>
       <c r="J287" t="n">
-        <v>19.758</v>
+        <v>17.619</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.14</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2295</v>
+        <v>0.1836</v>
       </c>
       <c r="J288" t="n">
-        <v>6.885</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2166</v>
+        <v>0.1724</v>
       </c>
       <c r="J289" t="n">
-        <v>6.498</v>
+        <v>5.172</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0089</v>
+        <v>-0.0066</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.267</v>
+        <v>-0.198</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2124</v>
+        <v>-0.1923</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.372</v>
+        <v>-5.769</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0918</v>
+        <v>1.1028</v>
       </c>
       <c r="J292" t="n">
-        <v>29.4786</v>
+        <v>29.7756</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6839</v>
+        <v>0.6508</v>
       </c>
       <c r="J293" t="n">
-        <v>18.4653</v>
+        <v>17.5716</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3945</v>
+        <v>0.3571</v>
       </c>
       <c r="J294" t="n">
-        <v>10.6515</v>
+        <v>9.6417</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2558</v>
+        <v>-0.2169</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.9066</v>
+        <v>-5.8563</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.86</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4708</v>
+        <v>-0.4292</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.7116</v>
+        <v>-11.5884</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.23</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5007</v>
+        <v>0.4431</v>
       </c>
       <c r="J297" t="n">
-        <v>13.5189</v>
+        <v>11.9637</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.99</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0214</v>
+        <v>-0.0159</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.5778</v>
+        <v>-0.4293</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0824</v>
+        <v>-0.0683</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.2248</v>
+        <v>-1.8441</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.87</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.7223</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.66</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3786</v>
+        <v>-0.3659</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.2222</v>
+        <v>-9.879300000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.57</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1975</v>
+        <v>1.2124</v>
       </c>
       <c r="J302" t="n">
-        <v>32.3325</v>
+        <v>32.7348</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.35</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8511</v>
+        <v>0.8304</v>
       </c>
       <c r="J303" t="n">
-        <v>22.9797</v>
+        <v>22.4208</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I304" t="n">
-        <v>0.501</v>
+        <v>0.4668</v>
       </c>
       <c r="J304" t="n">
-        <v>13.527</v>
+        <v>12.6036</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1681</v>
+        <v>0.142</v>
       </c>
       <c r="J305" t="n">
-        <v>4.5387</v>
+        <v>3.834</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4079</v>
+        <v>-0.367</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.0133</v>
+        <v>-9.909000000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6425</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J307" t="n">
-        <v>17.3475</v>
+        <v>15.8274</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2613</v>
+        <v>0.2136</v>
       </c>
       <c r="J308" t="n">
-        <v>7.0551</v>
+        <v>5.7672</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1432</v>
+        <v>-0.1243</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.8664</v>
+        <v>-3.3561</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.187</v>
+        <v>-0.1667</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.049</v>
+        <v>-4.5009</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.6</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4335</v>
+        <v>-0.4263</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.7045</v>
+        <v>-11.5101</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.27</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3815</v>
+        <v>0.3207</v>
       </c>
       <c r="J312" t="n">
-        <v>13.3525</v>
+        <v>11.2245</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3586</v>
+        <v>0.2998</v>
       </c>
       <c r="J313" t="n">
-        <v>12.551</v>
+        <v>10.493</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2133</v>
+        <v>0.1707</v>
       </c>
       <c r="J314" t="n">
-        <v>7.4655</v>
+        <v>5.9745</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.13</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2133</v>
+        <v>0.1707</v>
       </c>
       <c r="J315" t="n">
-        <v>7.4655</v>
+        <v>5.9745</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.12</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1998</v>
+        <v>0.1591</v>
       </c>
       <c r="J316" t="n">
-        <v>6.993</v>
+        <v>5.5685</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2491</v>
+        <v>0.2352</v>
       </c>
       <c r="J317" t="n">
-        <v>8.718500000000001</v>
+        <v>8.231999999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0137</v>
+        <v>0.011</v>
       </c>
       <c r="J318" t="n">
-        <v>0.4795</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.95</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.078</v>
+        <v>-0.0653</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.73</v>
+        <v>-2.2855</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3091</v>
+        <v>-0.2914</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.8185</v>
+        <v>-10.199</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3916</v>
+        <v>-0.3796</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.706</v>
+        <v>-13.286</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4539</v>
+        <v>0.4033</v>
       </c>
       <c r="J322" t="n">
-        <v>11.3475</v>
+        <v>10.0825</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.83</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2071</v>
+        <v>-0.1893</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.1775</v>
+        <v>-4.7325</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2263</v>
+        <v>-0.2082</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.6575</v>
+        <v>-5.205</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3024</v>
+        <v>-0.285</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.56</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.57</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4471</v>
+        <v>-0.4401</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.1775</v>
+        <v>-11.0025</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.72</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3539</v>
+        <v>1.3762</v>
       </c>
       <c r="J327" t="n">
-        <v>33.8475</v>
+        <v>34.405</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1122</v>
+        <v>1.1266</v>
       </c>
       <c r="J328" t="n">
-        <v>27.805</v>
+        <v>28.165</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.52</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0991</v>
+        <v>1.1131</v>
       </c>
       <c r="J329" t="n">
-        <v>27.4775</v>
+        <v>27.8275</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.35</v>
       </c>
       <c r="I330" t="n">
-        <v>0.8259</v>
+        <v>0.8122</v>
       </c>
       <c r="J330" t="n">
-        <v>20.6475</v>
+        <v>20.305</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6075</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.1875</v>
+        <v>-14.4525</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.18</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3971</v>
+        <v>0.3409</v>
       </c>
       <c r="J332" t="n">
-        <v>16.6782</v>
+        <v>14.3178</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.09</v>
       </c>
       <c r="I333" t="n">
-        <v>0.231</v>
+        <v>0.1868</v>
       </c>
       <c r="J333" t="n">
-        <v>9.702</v>
+        <v>7.8456</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.06</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1687</v>
+        <v>0.1319</v>
       </c>
       <c r="J334" t="n">
-        <v>7.0854</v>
+        <v>5.5398</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.03</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0988</v>
+        <v>0.0732</v>
       </c>
       <c r="J335" t="n">
-        <v>4.1496</v>
+        <v>3.0744</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3577</v>
+        <v>-0.3438</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.0234</v>
+        <v>-14.4396</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.57</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2291</v>
+        <v>1.2486</v>
       </c>
       <c r="J337" t="n">
-        <v>51.6222</v>
+        <v>52.4412</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.325</v>
+        <v>0.2874</v>
       </c>
       <c r="J338" t="n">
-        <v>13.65</v>
+        <v>12.0708</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2458</v>
+        <v>0.2124</v>
       </c>
       <c r="J339" t="n">
-        <v>10.3236</v>
+        <v>8.9208</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.89</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3866</v>
+        <v>-0.3437</v>
       </c>
       <c r="J340" t="n">
-        <v>-16.2372</v>
+        <v>-14.4354</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.83</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5357</v>
+        <v>-0.4952</v>
       </c>
       <c r="J341" t="n">
-        <v>-22.4994</v>
+        <v>-20.7984</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.26</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.4736</v>
       </c>
       <c r="J342" t="n">
-        <v>15.4512</v>
+        <v>13.7344</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.03</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0997</v>
+        <v>0.0737</v>
       </c>
       <c r="J343" t="n">
-        <v>2.8913</v>
+        <v>2.1373</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.99</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0253</v>
+        <v>-0.0182</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.7337</v>
+        <v>-0.5278</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1695</v>
+        <v>-0.1492</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.9155</v>
+        <v>-4.3268</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2017</v>
+        <v>-0.181</v>
       </c>
       <c r="J346" t="n">
-        <v>-5.8493</v>
+        <v>-5.249</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6515</v>
+        <v>0.6157</v>
       </c>
       <c r="J347" t="n">
-        <v>18.8935</v>
+        <v>17.8553</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.17</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4947</v>
+        <v>0.4545</v>
       </c>
       <c r="J348" t="n">
-        <v>14.3463</v>
+        <v>13.1805</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.17</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4947</v>
+        <v>0.4545</v>
       </c>
       <c r="J349" t="n">
-        <v>14.3463</v>
+        <v>13.1805</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1149</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.3321</v>
+        <v>-2.5636</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.89</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3862</v>
+        <v>-0.3433</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.1998</v>
+        <v>-9.9557</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.92</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.083</v>
+        <v>-0.0665</v>
       </c>
       <c r="J352" t="n">
-        <v>-1.66</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.91</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.914</v>
+        <v>-1.584</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.7</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.3167</v>
+        <v>-0.3034</v>
       </c>
       <c r="J354" t="n">
-        <v>-6.334</v>
+        <v>-6.068</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.55</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.4485</v>
+        <v>-0.4414</v>
       </c>
       <c r="J355" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.827999999999999</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.36</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.6143</v>
+        <v>-0.6293</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.286</v>
+        <v>-12.586</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3671</v>
+        <v>1.3901</v>
       </c>
       <c r="J357" t="n">
-        <v>27.342</v>
+        <v>27.802</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.66</v>
       </c>
       <c r="I358" t="n">
-        <v>1.2795</v>
+        <v>1.2982</v>
       </c>
       <c r="J358" t="n">
-        <v>25.59</v>
+        <v>25.964</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.3</v>
       </c>
       <c r="I359" t="n">
-        <v>0.7295</v>
+        <v>0.71</v>
       </c>
       <c r="J359" t="n">
-        <v>14.59</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.26</v>
       </c>
       <c r="I360" t="n">
-        <v>0.6483</v>
+        <v>0.6248</v>
       </c>
       <c r="J360" t="n">
-        <v>12.966</v>
+        <v>12.496</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2015</v>
+        <v>-0.1737</v>
       </c>
       <c r="J361" t="n">
-        <v>-4.03</v>
+        <v>-3.474</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.76</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4024</v>
+        <v>1.4273</v>
       </c>
       <c r="J362" t="n">
-        <v>29.4504</v>
+        <v>29.9733</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.73</v>
       </c>
       <c r="I363" t="n">
-        <v>1.3653</v>
+        <v>1.3882</v>
       </c>
       <c r="J363" t="n">
-        <v>28.6713</v>
+        <v>29.1522</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.37</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8628</v>
+        <v>0.8516</v>
       </c>
       <c r="J364" t="n">
-        <v>18.1188</v>
+        <v>17.8836</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.21</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5405</v>
+        <v>0.5127</v>
       </c>
       <c r="J365" t="n">
-        <v>11.3505</v>
+        <v>10.7667</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.9</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4108</v>
+        <v>-0.3755</v>
       </c>
       <c r="J366" t="n">
-        <v>-8.626799999999999</v>
+        <v>-7.8855</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>0.93</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.0723</v>
+        <v>-0.0566</v>
       </c>
       <c r="J367" t="n">
-        <v>-1.5183</v>
+        <v>-1.1886</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.91</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.082</v>
       </c>
       <c r="J368" t="n">
-        <v>-2.0601</v>
+        <v>-1.722</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.63</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3789</v>
+        <v>-0.3669</v>
       </c>
       <c r="J369" t="n">
-        <v>-7.9569</v>
+        <v>-7.7049</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.53</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4674</v>
+        <v>-0.4621</v>
       </c>
       <c r="J370" t="n">
-        <v>-9.8154</v>
+        <v>-9.7041</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.49</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5011</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.5525</v>
+        <v>-10.5231</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.78</v>
       </c>
       <c r="I372" t="n">
-        <v>1.4306</v>
+        <v>1.4573</v>
       </c>
       <c r="J372" t="n">
-        <v>32.9038</v>
+        <v>33.5179</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.63</v>
       </c>
       <c r="I373" t="n">
-        <v>1.2428</v>
+        <v>1.26</v>
       </c>
       <c r="J373" t="n">
-        <v>28.5844</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.27</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6701</v>
+        <v>0.6473</v>
       </c>
       <c r="J374" t="n">
-        <v>15.4123</v>
+        <v>14.8879</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.3332</v>
+        <v>0.3011</v>
       </c>
       <c r="J375" t="n">
-        <v>7.6636</v>
+        <v>6.9253</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>1.08</v>
       </c>
       <c r="I376" t="n">
-        <v>0.2281</v>
+        <v>0.1973</v>
       </c>
       <c r="J376" t="n">
-        <v>5.2463</v>
+        <v>4.5379</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.01</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1261</v>
+        <v>0.1129</v>
       </c>
       <c r="J377" t="n">
-        <v>2.9003</v>
+        <v>2.5967</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.83</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1913</v>
+        <v>-0.1758</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.3999</v>
+        <v>-4.0434</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.6</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.4061</v>
+        <v>-0.3956</v>
       </c>
       <c r="J379" t="n">
-        <v>-9.340299999999999</v>
+        <v>-9.098800000000001</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.58</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4238</v>
+        <v>-0.4146</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.747400000000001</v>
+        <v>-9.5358</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.49</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.503</v>
+        <v>-0.5017</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.569</v>
+        <v>-11.5391</v>
       </c>
     </row>
   </sheetData>
